--- a/AAII_Financials/Quarterly/MKFG_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/MKFG_QTR_FIN.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Stocks_Automation\AAII_Financials\Quarterly\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Private\Investing\Automation\AAII\AAII_Financials\Quarterly\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -17,7 +17,7 @@
   <definedNames>
     <definedName name="Ticker">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="152511" calcMode="manual" concurrentCalc="0"/>
+  <calcPr calcId="152511" calcMode="manual"/>
 </workbook>
 </file>
 

--- a/AAII_Financials/Quarterly/MKFG_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/MKFG_QTR_FIN.xlsx
@@ -656,136 +656,143 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:U102"/>
+  <dimension ref="A5:W102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="21" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="23" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:23" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E7" s="2">
+        <v>45291</v>
+      </c>
+      <c r="F7" s="2">
         <v>45199</v>
       </c>
-      <c r="E7" s="2">
+      <c r="G7" s="2">
         <v>45107</v>
       </c>
-      <c r="F7" s="2">
+      <c r="H7" s="2">
         <v>45016</v>
       </c>
-      <c r="G7" s="2">
+      <c r="I7" s="2">
         <v>44926</v>
       </c>
-      <c r="H7" s="2">
+      <c r="J7" s="2">
         <v>44834</v>
       </c>
-      <c r="I7" s="2">
+      <c r="K7" s="2">
         <v>44742</v>
       </c>
-      <c r="J7" s="2">
+      <c r="L7" s="2">
         <v>44651</v>
       </c>
-      <c r="K7" s="2">
+      <c r="M7" s="2">
         <v>44561</v>
       </c>
-      <c r="L7" s="2">
+      <c r="N7" s="2">
         <v>44469</v>
       </c>
-      <c r="M7" s="2">
+      <c r="O7" s="2">
         <v>44377</v>
       </c>
-      <c r="N7" s="2">
+      <c r="P7" s="2">
         <v>44286</v>
       </c>
-      <c r="O7" s="2">
+      <c r="Q7" s="2">
         <v>44196</v>
       </c>
-      <c r="P7" s="2">
+      <c r="R7" s="2">
         <v>44104</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="S7" s="2">
         <v>44012</v>
       </c>
-      <c r="R7" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="S7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="T7" s="2" t="s">
         <v>3</v>
       </c>
       <c r="U7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V7" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="W7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>20500</v>
+      </c>
+      <c r="E8" s="3">
+        <v>24200</v>
+      </c>
+      <c r="F8" s="3">
         <v>20100</v>
       </c>
-      <c r="E8" s="3">
+      <c r="G8" s="3">
         <v>25400</v>
       </c>
-      <c r="F8" s="3">
+      <c r="H8" s="3">
         <v>24100</v>
       </c>
-      <c r="G8" s="3">
+      <c r="I8" s="3">
         <v>29700</v>
       </c>
-      <c r="H8" s="3">
+      <c r="J8" s="3">
         <v>25200</v>
       </c>
-      <c r="I8" s="3">
+      <c r="K8" s="3">
         <v>24200</v>
       </c>
-      <c r="J8" s="3">
+      <c r="L8" s="3">
         <v>21900</v>
       </c>
-      <c r="K8" s="3">
+      <c r="M8" s="3">
         <v>26600</v>
       </c>
-      <c r="L8" s="3">
+      <c r="N8" s="3">
         <v>24000</v>
       </c>
-      <c r="M8" s="3">
+      <c r="O8" s="3">
         <v>40500</v>
       </c>
-      <c r="N8" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P8" s="3" t="s">
         <v>3</v>
       </c>
@@ -795,56 +802,62 @@
       <c r="R8" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="S8" s="3">
-        <v>0</v>
-      </c>
-      <c r="T8" s="3">
-        <v>0</v>
+      <c r="S8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T8" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="U8" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V8" s="3">
+        <v>0</v>
+      </c>
+      <c r="W8" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>10400</v>
+      </c>
+      <c r="E9" s="3">
+        <v>12500</v>
+      </c>
+      <c r="F9" s="3">
         <v>10900</v>
       </c>
-      <c r="E9" s="3">
+      <c r="G9" s="3">
         <v>13500</v>
       </c>
-      <c r="F9" s="3">
+      <c r="H9" s="3">
         <v>12500</v>
       </c>
-      <c r="G9" s="3">
+      <c r="I9" s="3">
         <v>15700</v>
       </c>
-      <c r="H9" s="3">
+      <c r="J9" s="3">
         <v>13000</v>
       </c>
-      <c r="I9" s="3">
+      <c r="K9" s="3">
         <v>11300</v>
-      </c>
-      <c r="J9" s="3">
-        <v>10300</v>
-      </c>
-      <c r="K9" s="3">
-        <v>11600</v>
       </c>
       <c r="L9" s="3">
         <v>10300</v>
       </c>
       <c r="M9" s="3">
+        <v>11600</v>
+      </c>
+      <c r="N9" s="3">
+        <v>10300</v>
+      </c>
+      <c r="O9" s="3">
         <v>16400</v>
       </c>
-      <c r="N9" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O9" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P9" s="3" t="s">
         <v>3</v>
       </c>
@@ -863,47 +876,53 @@
       <c r="U9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V9" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>10100</v>
+      </c>
+      <c r="E10" s="3">
+        <v>11700</v>
+      </c>
+      <c r="F10" s="3">
         <v>9200</v>
       </c>
-      <c r="E10" s="3">
+      <c r="G10" s="3">
         <v>11900</v>
       </c>
-      <c r="F10" s="3">
+      <c r="H10" s="3">
         <v>11600</v>
       </c>
-      <c r="G10" s="3">
+      <c r="I10" s="3">
         <v>14000</v>
       </c>
-      <c r="H10" s="3">
+      <c r="J10" s="3">
         <v>12200</v>
       </c>
-      <c r="I10" s="3">
+      <c r="K10" s="3">
         <v>12900</v>
       </c>
-      <c r="J10" s="3">
+      <c r="L10" s="3">
         <v>11600</v>
       </c>
-      <c r="K10" s="3">
+      <c r="M10" s="3">
         <v>15000</v>
       </c>
-      <c r="L10" s="3">
+      <c r="N10" s="3">
         <v>13700</v>
       </c>
-      <c r="M10" s="3">
+      <c r="O10" s="3">
         <v>24100</v>
       </c>
-      <c r="N10" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P10" s="3" t="s">
         <v>3</v>
       </c>
@@ -922,8 +941,14 @@
       <c r="U10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V10" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -945,47 +970,49 @@
       <c r="S11" s="3"/>
       <c r="T11" s="3"/>
       <c r="U11" s="3"/>
-    </row>
-    <row r="12" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V11" s="3"/>
+      <c r="W11" s="3"/>
+    </row>
+    <row r="12" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
-        <v>9700</v>
+        <v>9900</v>
       </c>
       <c r="E12" s="3">
         <v>10300</v>
       </c>
       <c r="F12" s="3">
-        <v>10400</v>
+        <v>9700</v>
       </c>
       <c r="G12" s="3">
-        <v>11000</v>
+        <v>10300</v>
       </c>
       <c r="H12" s="3">
         <v>10400</v>
       </c>
       <c r="I12" s="3">
+        <v>11000</v>
+      </c>
+      <c r="J12" s="3">
         <v>10400</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
+        <v>10400</v>
+      </c>
+      <c r="L12" s="3">
         <v>10600</v>
       </c>
-      <c r="K12" s="3">
+      <c r="M12" s="3">
         <v>10700</v>
       </c>
-      <c r="L12" s="3">
+      <c r="N12" s="3">
         <v>9800</v>
       </c>
-      <c r="M12" s="3">
+      <c r="O12" s="3">
         <v>11700</v>
       </c>
-      <c r="N12" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O12" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P12" s="3" t="s">
         <v>3</v>
       </c>
@@ -1004,8 +1031,14 @@
       <c r="U12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V12" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1063,22 +1096,28 @@
       <c r="U13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V13" s="3">
+        <v>0</v>
+      </c>
+      <c r="W13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>17300</v>
+      </c>
+      <c r="E14" s="3">
+        <v>0</v>
+      </c>
+      <c r="F14" s="3">
         <v>29500</v>
       </c>
-      <c r="E14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G14" s="3" t="s">
-        <v>3</v>
+      <c r="G14" s="3">
+        <v>4000</v>
       </c>
       <c r="H14" s="3" t="s">
         <v>3</v>
@@ -1089,11 +1128,11 @@
       <c r="J14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K14" s="3">
-        <v>0</v>
-      </c>
-      <c r="L14" s="3">
-        <v>0</v>
+      <c r="K14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M14" s="3">
         <v>0</v>
@@ -1122,8 +1161,14 @@
       <c r="U14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V14" s="3">
+        <v>0</v>
+      </c>
+      <c r="W14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1181,8 +1226,14 @@
       <c r="U15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V15" s="3">
+        <v>0</v>
+      </c>
+      <c r="W15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:23" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1201,58 +1252,60 @@
       <c r="S16" s="3"/>
       <c r="T16" s="3"/>
       <c r="U16" s="3"/>
-    </row>
-    <row r="17" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V16" s="3"/>
+      <c r="W16" s="3"/>
+    </row>
+    <row r="17" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>57700</v>
+      </c>
+      <c r="E17" s="3">
+        <v>43500</v>
+      </c>
+      <c r="F17" s="3">
         <v>70500</v>
       </c>
-      <c r="E17" s="3">
+      <c r="G17" s="3">
         <v>45500</v>
       </c>
-      <c r="F17" s="3">
+      <c r="H17" s="3">
         <v>45600</v>
       </c>
-      <c r="G17" s="3">
+      <c r="I17" s="3">
         <v>49000</v>
       </c>
-      <c r="H17" s="3">
+      <c r="J17" s="3">
         <v>48000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="K17" s="3">
         <v>48000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="L17" s="3">
         <v>43000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="M17" s="3">
         <v>45600</v>
       </c>
-      <c r="L17" s="3">
+      <c r="N17" s="3">
         <v>46400</v>
       </c>
-      <c r="M17" s="3">
+      <c r="O17" s="3">
         <v>60300</v>
       </c>
-      <c r="N17" s="3">
+      <c r="P17" s="3">
         <v>2100</v>
       </c>
-      <c r="O17" s="3">
+      <c r="Q17" s="3">
         <v>200</v>
       </c>
-      <c r="P17" s="3">
+      <c r="R17" s="3">
         <v>200</v>
       </c>
-      <c r="Q17" s="3">
-        <v>0</v>
-      </c>
-      <c r="R17" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S17" s="3" t="s">
-        <v>3</v>
+      <c r="S17" s="3">
+        <v>0</v>
       </c>
       <c r="T17" s="3" t="s">
         <v>3</v>
@@ -1260,47 +1313,53 @@
       <c r="U17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V17" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-37200</v>
+      </c>
+      <c r="E18" s="3">
+        <v>-19300</v>
+      </c>
+      <c r="F18" s="3">
         <v>-50400</v>
       </c>
-      <c r="E18" s="3">
+      <c r="G18" s="3">
         <v>-20100</v>
       </c>
-      <c r="F18" s="3">
+      <c r="H18" s="3">
         <v>-21500</v>
       </c>
-      <c r="G18" s="3">
+      <c r="I18" s="3">
         <v>-19300</v>
       </c>
-      <c r="H18" s="3">
+      <c r="J18" s="3">
         <v>-22800</v>
       </c>
-      <c r="I18" s="3">
+      <c r="K18" s="3">
         <v>-23800</v>
       </c>
-      <c r="J18" s="3">
+      <c r="L18" s="3">
         <v>-21100</v>
       </c>
-      <c r="K18" s="3">
+      <c r="M18" s="3">
         <v>-19000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="N18" s="3">
         <v>-22400</v>
       </c>
-      <c r="M18" s="3">
+      <c r="O18" s="3">
         <v>-19800</v>
       </c>
-      <c r="N18" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P18" s="3" t="s">
         <v>3</v>
       </c>
@@ -1319,8 +1378,14 @@
       <c r="U18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1342,47 +1407,49 @@
       <c r="S19" s="3"/>
       <c r="T19" s="3"/>
       <c r="U19" s="3"/>
-    </row>
-    <row r="20" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V19" s="3"/>
+      <c r="W19" s="3"/>
+    </row>
+    <row r="20" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>1200</v>
+      </c>
+      <c r="E20" s="3">
+        <v>5300</v>
+      </c>
+      <c r="F20" s="3">
         <v>-1100</v>
       </c>
-      <c r="E20" s="3">
+      <c r="G20" s="3">
         <v>900</v>
       </c>
-      <c r="F20" s="3">
+      <c r="H20" s="3">
         <v>2500</v>
       </c>
-      <c r="G20" s="3">
+      <c r="I20" s="3">
         <v>8100</v>
       </c>
-      <c r="H20" s="3">
+      <c r="J20" s="3">
         <v>-100</v>
       </c>
-      <c r="I20" s="3">
+      <c r="K20" s="3">
         <v>27900</v>
       </c>
-      <c r="J20" s="3">
+      <c r="L20" s="3">
         <v>25300</v>
       </c>
-      <c r="K20" s="3">
+      <c r="M20" s="3">
         <v>22300</v>
       </c>
-      <c r="L20" s="3">
+      <c r="N20" s="3">
         <v>44100</v>
       </c>
-      <c r="M20" s="3">
+      <c r="O20" s="3">
         <v>-1300</v>
       </c>
-      <c r="N20" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P20" s="3" t="s">
         <v>3</v>
       </c>
@@ -1401,41 +1468,47 @@
       <c r="U20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-32900</v>
+      </c>
+      <c r="E21" s="3">
+        <v>-10900</v>
+      </c>
+      <c r="F21" s="3">
         <v>-48600</v>
       </c>
-      <c r="E21" s="3">
+      <c r="G21" s="3">
         <v>-15000</v>
       </c>
-      <c r="F21" s="3">
+      <c r="H21" s="3">
         <v>-16600</v>
       </c>
-      <c r="G21" s="3">
+      <c r="I21" s="3">
         <v>-8300</v>
       </c>
-      <c r="H21" s="3">
+      <c r="J21" s="3">
         <v>-20300</v>
       </c>
-      <c r="I21" s="3">
+      <c r="K21" s="3">
         <v>6600</v>
       </c>
-      <c r="J21" s="3">
+      <c r="L21" s="3">
         <v>5400</v>
       </c>
-      <c r="K21" s="3">
+      <c r="M21" s="3">
         <v>3800</v>
       </c>
-      <c r="L21" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N21" s="3" t="s">
         <v>3</v>
       </c>
@@ -1460,25 +1533,31 @@
       <c r="U21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="E22" s="3">
         <v>100</v>
       </c>
-      <c r="F22" s="3" t="s">
-        <v>3</v>
+      <c r="F22" s="3">
+        <v>100</v>
       </c>
       <c r="G22" s="3">
-        <v>0</v>
-      </c>
-      <c r="H22" s="3">
-        <v>0</v>
+        <v>100</v>
+      </c>
+      <c r="H22" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="I22" s="3">
         <v>0</v>
@@ -1495,11 +1574,11 @@
       <c r="M22" s="3">
         <v>0</v>
       </c>
-      <c r="N22" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O22" s="3" t="s">
-        <v>3</v>
+      <c r="N22" s="3">
+        <v>0</v>
+      </c>
+      <c r="O22" s="3">
+        <v>0</v>
       </c>
       <c r="P22" s="3" t="s">
         <v>3</v>
@@ -1510,67 +1589,73 @@
       <c r="R22" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="S22" s="3">
-        <v>0</v>
-      </c>
-      <c r="T22" s="3">
-        <v>0</v>
+      <c r="S22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T22" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="U22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V22" s="3">
+        <v>0</v>
+      </c>
+      <c r="W22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-36100</v>
+      </c>
+      <c r="E23" s="3">
+        <v>-14200</v>
+      </c>
+      <c r="F23" s="3">
         <v>-51600</v>
       </c>
-      <c r="E23" s="3">
+      <c r="G23" s="3">
         <v>-19300</v>
       </c>
-      <c r="F23" s="3">
+      <c r="H23" s="3">
         <v>-19000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="I23" s="3">
         <v>-11200</v>
       </c>
-      <c r="H23" s="3">
+      <c r="J23" s="3">
         <v>-23000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="K23" s="3">
         <v>4100</v>
       </c>
-      <c r="J23" s="3">
+      <c r="L23" s="3">
         <v>4200</v>
       </c>
-      <c r="K23" s="3">
+      <c r="M23" s="3">
         <v>3300</v>
       </c>
-      <c r="L23" s="3">
+      <c r="N23" s="3">
         <v>21700</v>
       </c>
-      <c r="M23" s="3">
+      <c r="O23" s="3">
         <v>-21100</v>
       </c>
-      <c r="N23" s="3">
+      <c r="P23" s="3">
         <v>-6900</v>
       </c>
-      <c r="O23" s="3">
+      <c r="Q23" s="3">
         <v>-2400</v>
       </c>
-      <c r="P23" s="3">
+      <c r="R23" s="3">
         <v>-200</v>
       </c>
-      <c r="Q23" s="3">
-        <v>0</v>
-      </c>
-      <c r="R23" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S23" s="3" t="s">
-        <v>3</v>
+      <c r="S23" s="3">
+        <v>0</v>
       </c>
       <c r="T23" s="3" t="s">
         <v>3</v>
@@ -1578,8 +1663,14 @@
       <c r="U23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V23" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1587,10 +1678,10 @@
         <v>-200</v>
       </c>
       <c r="E24" s="3">
-        <v>-400</v>
+        <v>0</v>
       </c>
       <c r="F24" s="3">
-        <v>0</v>
+        <v>-200</v>
       </c>
       <c r="G24" s="3">
         <v>-400</v>
@@ -1599,25 +1690,25 @@
         <v>0</v>
       </c>
       <c r="I24" s="3">
-        <v>0</v>
+        <v>-400</v>
       </c>
       <c r="J24" s="3">
         <v>0</v>
       </c>
       <c r="K24" s="3">
+        <v>0</v>
+      </c>
+      <c r="L24" s="3">
+        <v>0</v>
+      </c>
+      <c r="M24" s="3">
         <v>100</v>
       </c>
-      <c r="L24" s="3">
-        <v>0</v>
-      </c>
-      <c r="M24" s="3">
-        <v>0</v>
-      </c>
-      <c r="N24" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O24" s="3" t="s">
-        <v>3</v>
+      <c r="N24" s="3">
+        <v>0</v>
+      </c>
+      <c r="O24" s="3">
+        <v>0</v>
       </c>
       <c r="P24" s="3" t="s">
         <v>3</v>
@@ -1628,17 +1719,23 @@
       <c r="R24" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="S24" s="3">
-        <v>0</v>
-      </c>
-      <c r="T24" s="3">
-        <v>0</v>
+      <c r="S24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T24" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="U24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V24" s="3">
+        <v>0</v>
+      </c>
+      <c r="W24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1696,58 +1793,64 @@
       <c r="U25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V25" s="3">
+        <v>0</v>
+      </c>
+      <c r="W25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-35900</v>
+      </c>
+      <c r="E26" s="3">
+        <v>-14200</v>
+      </c>
+      <c r="F26" s="3">
         <v>-51400</v>
       </c>
-      <c r="E26" s="3">
+      <c r="G26" s="3">
         <v>-19000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="H26" s="3">
         <v>-19000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="I26" s="3">
         <v>-10700</v>
       </c>
-      <c r="H26" s="3">
+      <c r="J26" s="3">
         <v>-23000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="K26" s="3">
         <v>4100</v>
       </c>
-      <c r="J26" s="3">
+      <c r="L26" s="3">
         <v>4200</v>
       </c>
-      <c r="K26" s="3">
+      <c r="M26" s="3">
         <v>3300</v>
       </c>
-      <c r="L26" s="3">
+      <c r="N26" s="3">
         <v>21700</v>
       </c>
-      <c r="M26" s="3">
+      <c r="O26" s="3">
         <v>-21100</v>
       </c>
-      <c r="N26" s="3">
+      <c r="P26" s="3">
         <v>-6900</v>
       </c>
-      <c r="O26" s="3">
+      <c r="Q26" s="3">
         <v>-2400</v>
       </c>
-      <c r="P26" s="3">
+      <c r="R26" s="3">
         <v>-200</v>
       </c>
-      <c r="Q26" s="3">
-        <v>0</v>
-      </c>
-      <c r="R26" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S26" s="3" t="s">
-        <v>3</v>
+      <c r="S26" s="3">
+        <v>0</v>
       </c>
       <c r="T26" s="3" t="s">
         <v>3</v>
@@ -1755,58 +1858,64 @@
       <c r="U26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V26" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-35900</v>
+      </c>
+      <c r="E27" s="3">
+        <v>-14200</v>
+      </c>
+      <c r="F27" s="3">
         <v>-51400</v>
       </c>
-      <c r="E27" s="3">
+      <c r="G27" s="3">
         <v>-19000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="H27" s="3">
         <v>-19000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="I27" s="3">
         <v>-10700</v>
       </c>
-      <c r="H27" s="3">
+      <c r="J27" s="3">
         <v>-23000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="K27" s="3">
         <v>4100</v>
       </c>
-      <c r="J27" s="3">
+      <c r="L27" s="3">
         <v>4200</v>
       </c>
-      <c r="K27" s="3">
+      <c r="M27" s="3">
         <v>3300</v>
       </c>
-      <c r="L27" s="3">
+      <c r="N27" s="3">
         <v>21700</v>
       </c>
-      <c r="M27" s="3">
+      <c r="O27" s="3">
         <v>-21100</v>
       </c>
-      <c r="N27" s="3">
+      <c r="P27" s="3">
         <v>-6900</v>
       </c>
-      <c r="O27" s="3">
+      <c r="Q27" s="3">
         <v>-2400</v>
       </c>
-      <c r="P27" s="3">
+      <c r="R27" s="3">
         <v>-200</v>
       </c>
-      <c r="Q27" s="3">
-        <v>0</v>
-      </c>
-      <c r="R27" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S27" s="3" t="s">
-        <v>3</v>
+      <c r="S27" s="3">
+        <v>0</v>
       </c>
       <c r="T27" s="3" t="s">
         <v>3</v>
@@ -1814,8 +1923,14 @@
       <c r="U27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V27" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1873,8 +1988,14 @@
       <c r="U28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V28" s="3">
+        <v>0</v>
+      </c>
+      <c r="W28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1932,8 +2053,14 @@
       <c r="U29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V29" s="3">
+        <v>0</v>
+      </c>
+      <c r="W29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1991,8 +2118,14 @@
       <c r="U30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V30" s="3">
+        <v>0</v>
+      </c>
+      <c r="W30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2050,47 +2183,53 @@
       <c r="U31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V31" s="3">
+        <v>0</v>
+      </c>
+      <c r="W31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-1200</v>
+      </c>
+      <c r="E32" s="3">
+        <v>-5300</v>
+      </c>
+      <c r="F32" s="3">
         <v>1100</v>
       </c>
-      <c r="E32" s="3">
+      <c r="G32" s="3">
         <v>-900</v>
       </c>
-      <c r="F32" s="3">
+      <c r="H32" s="3">
         <v>-2500</v>
       </c>
-      <c r="G32" s="3">
+      <c r="I32" s="3">
         <v>-8100</v>
       </c>
-      <c r="H32" s="3">
+      <c r="J32" s="3">
         <v>100</v>
       </c>
-      <c r="I32" s="3">
+      <c r="K32" s="3">
         <v>-27900</v>
       </c>
-      <c r="J32" s="3">
+      <c r="L32" s="3">
         <v>-25300</v>
       </c>
-      <c r="K32" s="3">
+      <c r="M32" s="3">
         <v>-22300</v>
       </c>
-      <c r="L32" s="3">
+      <c r="N32" s="3">
         <v>-44100</v>
       </c>
-      <c r="M32" s="3">
+      <c r="O32" s="3">
         <v>1300</v>
       </c>
-      <c r="N32" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P32" s="3" t="s">
         <v>3</v>
       </c>
@@ -2109,58 +2248,64 @@
       <c r="U32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-35900</v>
+      </c>
+      <c r="E33" s="3">
+        <v>-14200</v>
+      </c>
+      <c r="F33" s="3">
         <v>-51400</v>
       </c>
-      <c r="E33" s="3">
+      <c r="G33" s="3">
         <v>-19000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="H33" s="3">
         <v>-19000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="I33" s="3">
         <v>-10700</v>
       </c>
-      <c r="H33" s="3">
+      <c r="J33" s="3">
         <v>-23000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="K33" s="3">
         <v>4100</v>
       </c>
-      <c r="J33" s="3">
+      <c r="L33" s="3">
         <v>4200</v>
       </c>
-      <c r="K33" s="3">
+      <c r="M33" s="3">
         <v>3300</v>
       </c>
-      <c r="L33" s="3">
+      <c r="N33" s="3">
         <v>21700</v>
       </c>
-      <c r="M33" s="3">
+      <c r="O33" s="3">
         <v>-21100</v>
       </c>
-      <c r="N33" s="3">
+      <c r="P33" s="3">
         <v>-6900</v>
       </c>
-      <c r="O33" s="3">
+      <c r="Q33" s="3">
         <v>-2400</v>
       </c>
-      <c r="P33" s="3">
+      <c r="R33" s="3">
         <v>-200</v>
       </c>
-      <c r="Q33" s="3">
-        <v>0</v>
-      </c>
-      <c r="R33" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S33" s="3" t="s">
-        <v>3</v>
+      <c r="S33" s="3">
+        <v>0</v>
       </c>
       <c r="T33" s="3" t="s">
         <v>3</v>
@@ -2168,8 +2313,14 @@
       <c r="U33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V33" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2227,58 +2378,64 @@
       <c r="U34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V34" s="3">
+        <v>0</v>
+      </c>
+      <c r="W34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-35900</v>
+      </c>
+      <c r="E35" s="3">
+        <v>-14200</v>
+      </c>
+      <c r="F35" s="3">
         <v>-51400</v>
       </c>
-      <c r="E35" s="3">
+      <c r="G35" s="3">
         <v>-19000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="H35" s="3">
         <v>-19000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="I35" s="3">
         <v>-10700</v>
       </c>
-      <c r="H35" s="3">
+      <c r="J35" s="3">
         <v>-23000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="K35" s="3">
         <v>4100</v>
       </c>
-      <c r="J35" s="3">
+      <c r="L35" s="3">
         <v>4200</v>
       </c>
-      <c r="K35" s="3">
+      <c r="M35" s="3">
         <v>3300</v>
       </c>
-      <c r="L35" s="3">
+      <c r="N35" s="3">
         <v>21700</v>
       </c>
-      <c r="M35" s="3">
+      <c r="O35" s="3">
         <v>-21100</v>
       </c>
-      <c r="N35" s="3">
+      <c r="P35" s="3">
         <v>-6900</v>
       </c>
-      <c r="O35" s="3">
+      <c r="Q35" s="3">
         <v>-2400</v>
       </c>
-      <c r="P35" s="3">
+      <c r="R35" s="3">
         <v>-200</v>
       </c>
-      <c r="Q35" s="3">
-        <v>0</v>
-      </c>
-      <c r="R35" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S35" s="3" t="s">
-        <v>3</v>
+      <c r="S35" s="3">
+        <v>0</v>
       </c>
       <c r="T35" s="3" t="s">
         <v>3</v>
@@ -2286,72 +2443,84 @@
       <c r="U35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V35" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:23" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E38" s="2">
+        <v>45291</v>
+      </c>
+      <c r="F38" s="2">
         <v>45199</v>
       </c>
-      <c r="E38" s="2">
+      <c r="G38" s="2">
         <v>45107</v>
       </c>
-      <c r="F38" s="2">
+      <c r="H38" s="2">
         <v>45016</v>
       </c>
-      <c r="G38" s="2">
+      <c r="I38" s="2">
         <v>44926</v>
       </c>
-      <c r="H38" s="2">
+      <c r="J38" s="2">
         <v>44834</v>
       </c>
-      <c r="I38" s="2">
+      <c r="K38" s="2">
         <v>44742</v>
       </c>
-      <c r="J38" s="2">
+      <c r="L38" s="2">
         <v>44651</v>
       </c>
-      <c r="K38" s="2">
+      <c r="M38" s="2">
         <v>44561</v>
       </c>
-      <c r="L38" s="2">
+      <c r="N38" s="2">
         <v>44469</v>
       </c>
-      <c r="M38" s="2">
+      <c r="O38" s="2">
         <v>44377</v>
       </c>
-      <c r="N38" s="2">
+      <c r="P38" s="2">
         <v>44286</v>
       </c>
-      <c r="O38" s="2">
+      <c r="Q38" s="2">
         <v>44196</v>
       </c>
-      <c r="P38" s="2">
+      <c r="R38" s="2">
         <v>44104</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="S38" s="2">
         <v>44012</v>
       </c>
-      <c r="R38" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="S38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="T38" s="2" t="s">
         <v>3</v>
       </c>
       <c r="U38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V38" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="W38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2373,8 +2542,10 @@
       <c r="S39" s="3"/>
       <c r="T39" s="3"/>
       <c r="U39" s="3"/>
-    </row>
-    <row r="40" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V39" s="3"/>
+      <c r="W39" s="3"/>
+    </row>
+    <row r="40" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2396,56 +2567,58 @@
       <c r="S40" s="3"/>
       <c r="T40" s="3"/>
       <c r="U40" s="3"/>
-    </row>
-    <row r="41" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V40" s="3"/>
+      <c r="W40" s="3"/>
+    </row>
+    <row r="41" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>107900</v>
+      </c>
+      <c r="E41" s="3">
+        <v>116900</v>
+      </c>
+      <c r="F41" s="3">
         <v>98200</v>
       </c>
-      <c r="E41" s="3">
+      <c r="G41" s="3">
         <v>85700</v>
       </c>
-      <c r="F41" s="3">
+      <c r="H41" s="3">
         <v>90700</v>
       </c>
-      <c r="G41" s="3">
+      <c r="I41" s="3">
         <v>124200</v>
       </c>
-      <c r="H41" s="3">
+      <c r="J41" s="3">
         <v>181800</v>
       </c>
-      <c r="I41" s="3">
+      <c r="K41" s="3">
         <v>243200</v>
       </c>
-      <c r="J41" s="3">
+      <c r="L41" s="3">
         <v>269100</v>
       </c>
-      <c r="K41" s="3">
+      <c r="M41" s="3">
         <v>288600</v>
       </c>
-      <c r="L41" s="3">
+      <c r="N41" s="3">
         <v>296700</v>
       </c>
-      <c r="M41" s="3">
+      <c r="O41" s="3">
         <v>300</v>
       </c>
-      <c r="N41" s="3">
+      <c r="P41" s="3">
         <v>500</v>
       </c>
-      <c r="O41" s="3">
+      <c r="Q41" s="3">
         <v>900</v>
       </c>
-      <c r="P41" s="3">
+      <c r="R41" s="3">
         <v>1100</v>
       </c>
-      <c r="Q41" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S41" s="3" t="s">
         <v>3</v>
       </c>
@@ -2455,29 +2628,35 @@
       <c r="U41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V41" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="D42" s="3">
+      <c r="D42" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E42" s="3">
+        <v>0</v>
+      </c>
+      <c r="F42" s="3">
         <v>27800</v>
       </c>
-      <c r="E42" s="3">
+      <c r="G42" s="3">
         <v>50400</v>
       </c>
-      <c r="F42" s="3">
+      <c r="H42" s="3">
         <v>60800</v>
       </c>
-      <c r="G42" s="3">
+      <c r="I42" s="3">
         <v>43700</v>
       </c>
-      <c r="H42" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I42" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J42" s="3" t="s">
         <v>3</v>
       </c>
@@ -2490,11 +2669,11 @@
       <c r="M42" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N42" s="3">
-        <v>0</v>
-      </c>
-      <c r="O42" s="3">
-        <v>0</v>
+      <c r="N42" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O42" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="P42" s="3">
         <v>0</v>
@@ -2514,44 +2693,50 @@
       <c r="U42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V42" s="3">
+        <v>0</v>
+      </c>
+      <c r="W42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>21500</v>
+      </c>
+      <c r="E43" s="3">
+        <v>24100</v>
+      </c>
+      <c r="F43" s="3">
         <v>22300</v>
       </c>
-      <c r="E43" s="3">
+      <c r="G43" s="3">
         <v>27100</v>
       </c>
-      <c r="F43" s="3">
+      <c r="H43" s="3">
         <v>26100</v>
       </c>
-      <c r="G43" s="3">
+      <c r="I43" s="3">
         <v>29300</v>
       </c>
-      <c r="H43" s="3">
+      <c r="J43" s="3">
         <v>30100</v>
       </c>
-      <c r="I43" s="3">
+      <c r="K43" s="3">
         <v>26600</v>
       </c>
-      <c r="J43" s="3">
+      <c r="L43" s="3">
         <v>22800</v>
       </c>
-      <c r="K43" s="3">
+      <c r="M43" s="3">
         <v>26800</v>
       </c>
-      <c r="L43" s="3">
+      <c r="N43" s="3">
         <v>24100</v>
       </c>
-      <c r="M43" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O43" s="3" t="s">
         <v>3</v>
       </c>
@@ -2564,53 +2749,59 @@
       <c r="R43" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="S43" s="3">
-        <v>0</v>
-      </c>
-      <c r="T43" s="3">
-        <v>0</v>
+      <c r="S43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T43" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="U43" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V43" s="3">
+        <v>0</v>
+      </c>
+      <c r="W43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>23800</v>
+      </c>
+      <c r="E44" s="3">
+        <v>26800</v>
+      </c>
+      <c r="F44" s="3">
         <v>28700</v>
       </c>
-      <c r="E44" s="3">
+      <c r="G44" s="3">
         <v>29600</v>
       </c>
-      <c r="F44" s="3">
+      <c r="H44" s="3">
         <v>29300</v>
       </c>
-      <c r="G44" s="3">
+      <c r="I44" s="3">
         <v>26400</v>
       </c>
-      <c r="H44" s="3">
+      <c r="J44" s="3">
         <v>24600</v>
       </c>
-      <c r="I44" s="3">
+      <c r="K44" s="3">
         <v>19300</v>
       </c>
-      <c r="J44" s="3">
+      <c r="L44" s="3">
         <v>12800</v>
       </c>
-      <c r="K44" s="3">
+      <c r="M44" s="3">
         <v>10400</v>
       </c>
-      <c r="L44" s="3">
+      <c r="N44" s="3">
         <v>11300</v>
       </c>
-      <c r="M44" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N44" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O44" s="3" t="s">
         <v>3</v>
       </c>
@@ -2623,135 +2814,153 @@
       <c r="R44" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="S44" s="3">
-        <v>0</v>
-      </c>
-      <c r="T44" s="3">
-        <v>0</v>
+      <c r="S44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T44" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="U44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V44" s="3">
+        <v>0</v>
+      </c>
+      <c r="W44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>5100</v>
+      </c>
+      <c r="E45" s="3">
+        <v>4800</v>
+      </c>
+      <c r="F45" s="3">
         <v>5500</v>
       </c>
-      <c r="E45" s="3">
+      <c r="G45" s="3">
         <v>4300</v>
       </c>
-      <c r="F45" s="3">
+      <c r="H45" s="3">
         <v>5700</v>
       </c>
-      <c r="G45" s="3">
+      <c r="I45" s="3">
         <v>6200</v>
       </c>
-      <c r="H45" s="3">
+      <c r="J45" s="3">
         <v>6600</v>
       </c>
-      <c r="I45" s="3">
+      <c r="K45" s="3">
         <v>3900</v>
       </c>
-      <c r="J45" s="3">
+      <c r="L45" s="3">
         <v>5500</v>
       </c>
-      <c r="K45" s="3">
+      <c r="M45" s="3">
         <v>4400</v>
       </c>
-      <c r="L45" s="3">
+      <c r="N45" s="3">
         <v>5900</v>
       </c>
-      <c r="M45" s="3">
+      <c r="O45" s="3">
         <v>200</v>
       </c>
-      <c r="N45" s="3">
+      <c r="P45" s="3">
         <v>300</v>
       </c>
-      <c r="O45" s="3">
+      <c r="Q45" s="3">
         <v>300</v>
       </c>
-      <c r="P45" s="3">
+      <c r="R45" s="3">
         <v>400</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="S45" s="3">
         <v>200</v>
       </c>
-      <c r="R45" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T45" s="3" t="s">
         <v>3</v>
       </c>
       <c r="U45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>158300</v>
+      </c>
+      <c r="E46" s="3">
+        <v>172500</v>
+      </c>
+      <c r="F46" s="3">
         <v>182500</v>
       </c>
-      <c r="E46" s="3">
+      <c r="G46" s="3">
         <v>197000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="H46" s="3">
         <v>212500</v>
       </c>
-      <c r="G46" s="3">
+      <c r="I46" s="3">
         <v>229800</v>
       </c>
-      <c r="H46" s="3">
+      <c r="J46" s="3">
         <v>243100</v>
       </c>
-      <c r="I46" s="3">
+      <c r="K46" s="3">
         <v>293000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="L46" s="3">
         <v>310300</v>
       </c>
-      <c r="K46" s="3">
+      <c r="M46" s="3">
         <v>330200</v>
       </c>
-      <c r="L46" s="3">
+      <c r="N46" s="3">
         <v>338000</v>
       </c>
-      <c r="M46" s="3">
+      <c r="O46" s="3">
         <v>600</v>
       </c>
-      <c r="N46" s="3">
+      <c r="P46" s="3">
         <v>800</v>
       </c>
-      <c r="O46" s="3">
+      <c r="Q46" s="3">
         <v>1200</v>
       </c>
-      <c r="P46" s="3">
+      <c r="R46" s="3">
         <v>1400</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="S46" s="3">
         <v>200</v>
       </c>
-      <c r="R46" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T46" s="3" t="s">
         <v>3</v>
       </c>
       <c r="U46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V46" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -2779,27 +2988,27 @@
       <c r="K47" s="3">
         <v>0</v>
       </c>
-      <c r="L47" s="3" t="s">
-        <v>3</v>
+      <c r="L47" s="3">
+        <v>0</v>
       </c>
       <c r="M47" s="3">
-        <v>215100</v>
-      </c>
-      <c r="N47" s="3">
-        <v>215100</v>
+        <v>0</v>
+      </c>
+      <c r="N47" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="O47" s="3">
         <v>215100</v>
       </c>
       <c r="P47" s="3">
+        <v>215100</v>
+      </c>
+      <c r="Q47" s="3">
+        <v>215100</v>
+      </c>
+      <c r="R47" s="3">
         <v>215000</v>
       </c>
-      <c r="Q47" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R47" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S47" s="3" t="s">
         <v>3</v>
       </c>
@@ -2809,44 +3018,50 @@
       <c r="U47" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="48" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W47" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="48" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>53700</v>
+      </c>
+      <c r="E48" s="3">
+        <v>54600</v>
+      </c>
+      <c r="F48" s="3">
         <v>55300</v>
       </c>
-      <c r="E48" s="3">
+      <c r="G48" s="3">
         <v>57600</v>
       </c>
-      <c r="F48" s="3">
+      <c r="H48" s="3">
         <v>63700</v>
       </c>
-      <c r="G48" s="3">
+      <c r="I48" s="3">
         <v>64300</v>
       </c>
-      <c r="H48" s="3">
+      <c r="J48" s="3">
         <v>59000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="K48" s="3">
         <v>53600</v>
       </c>
-      <c r="J48" s="3">
+      <c r="L48" s="3">
         <v>18400</v>
       </c>
-      <c r="K48" s="3">
+      <c r="M48" s="3">
         <v>6300</v>
       </c>
-      <c r="L48" s="3">
+      <c r="N48" s="3">
         <v>5300</v>
       </c>
-      <c r="M48" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O48" s="3" t="s">
         <v>3</v>
       </c>
@@ -2859,44 +3074,50 @@
       <c r="R48" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="S48" s="3">
-        <v>0</v>
-      </c>
-      <c r="T48" s="3">
-        <v>0</v>
+      <c r="S48" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T48" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="U48" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="49" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V48" s="3">
+        <v>0</v>
+      </c>
+      <c r="W48" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>15900</v>
+      </c>
+      <c r="E49" s="3">
+        <v>17100</v>
+      </c>
+      <c r="F49" s="3">
         <v>16200</v>
       </c>
-      <c r="E49" s="3">
+      <c r="G49" s="3">
         <v>46900</v>
       </c>
-      <c r="F49" s="3">
+      <c r="H49" s="3">
         <v>48600</v>
       </c>
-      <c r="G49" s="3">
+      <c r="I49" s="3">
         <v>48700</v>
       </c>
-      <c r="H49" s="3">
+      <c r="J49" s="3">
         <v>46600</v>
       </c>
-      <c r="I49" s="3">
+      <c r="K49" s="3">
         <v>6700</v>
       </c>
-      <c r="J49" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K49" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L49" s="3" t="s">
         <v>3</v>
       </c>
@@ -2906,11 +3127,11 @@
       <c r="N49" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O49" s="3">
-        <v>0</v>
-      </c>
-      <c r="P49" s="3">
-        <v>0</v>
+      <c r="O49" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P49" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Q49" s="3">
         <v>0</v>
@@ -2927,8 +3148,14 @@
       <c r="U49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V49" s="3">
+        <v>0</v>
+      </c>
+      <c r="W49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2986,8 +3213,14 @@
       <c r="U50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V50" s="3">
+        <v>0</v>
+      </c>
+      <c r="W50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3045,44 +3278,50 @@
       <c r="U51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V51" s="3">
+        <v>0</v>
+      </c>
+      <c r="W51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>3700</v>
+      </c>
+      <c r="E52" s="3">
+        <v>3800</v>
+      </c>
+      <c r="F52" s="3">
         <v>3500</v>
       </c>
-      <c r="E52" s="3">
+      <c r="G52" s="3">
         <v>3300</v>
       </c>
-      <c r="F52" s="3">
+      <c r="H52" s="3">
         <v>3000</v>
       </c>
-      <c r="G52" s="3">
+      <c r="I52" s="3">
         <v>3100</v>
       </c>
-      <c r="H52" s="3">
+      <c r="J52" s="3">
         <v>3200</v>
       </c>
-      <c r="I52" s="3">
+      <c r="K52" s="3">
         <v>2900</v>
       </c>
-      <c r="J52" s="3">
+      <c r="L52" s="3">
         <v>1000</v>
       </c>
-      <c r="K52" s="3">
+      <c r="M52" s="3">
         <v>800</v>
       </c>
-      <c r="L52" s="3">
+      <c r="N52" s="3">
         <v>800</v>
       </c>
-      <c r="M52" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O52" s="3" t="s">
         <v>3</v>
       </c>
@@ -3095,17 +3334,23 @@
       <c r="R52" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="S52" s="3">
-        <v>0</v>
-      </c>
-      <c r="T52" s="3">
-        <v>0</v>
+      <c r="S52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T52" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="U52" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="53" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V52" s="3">
+        <v>0</v>
+      </c>
+      <c r="W52" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3163,67 +3408,79 @@
       <c r="U53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V53" s="3">
+        <v>0</v>
+      </c>
+      <c r="W53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>231600</v>
+      </c>
+      <c r="E54" s="3">
+        <v>248000</v>
+      </c>
+      <c r="F54" s="3">
         <v>257400</v>
       </c>
-      <c r="E54" s="3">
+      <c r="G54" s="3">
         <v>304900</v>
       </c>
-      <c r="F54" s="3">
+      <c r="H54" s="3">
         <v>327900</v>
       </c>
-      <c r="G54" s="3">
+      <c r="I54" s="3">
         <v>345900</v>
       </c>
-      <c r="H54" s="3">
+      <c r="J54" s="3">
         <v>351900</v>
       </c>
-      <c r="I54" s="3">
+      <c r="K54" s="3">
         <v>356100</v>
       </c>
-      <c r="J54" s="3">
+      <c r="L54" s="3">
         <v>329700</v>
       </c>
-      <c r="K54" s="3">
+      <c r="M54" s="3">
         <v>337300</v>
       </c>
-      <c r="L54" s="3">
+      <c r="N54" s="3">
         <v>344100</v>
       </c>
-      <c r="M54" s="3">
+      <c r="O54" s="3">
         <v>215700</v>
       </c>
-      <c r="N54" s="3">
+      <c r="P54" s="3">
         <v>215900</v>
       </c>
-      <c r="O54" s="3">
+      <c r="Q54" s="3">
         <v>216300</v>
       </c>
-      <c r="P54" s="3">
+      <c r="R54" s="3">
         <v>216400</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="S54" s="3">
         <v>200</v>
       </c>
-      <c r="R54" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T54" s="3" t="s">
         <v>3</v>
       </c>
       <c r="U54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V54" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3245,8 +3502,10 @@
       <c r="S55" s="3"/>
       <c r="T55" s="3"/>
       <c r="U55" s="3"/>
-    </row>
-    <row r="56" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V55" s="3"/>
+      <c r="W55" s="3"/>
+    </row>
+    <row r="56" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3268,58 +3527,60 @@
       <c r="S56" s="3"/>
       <c r="T56" s="3"/>
       <c r="U56" s="3"/>
-    </row>
-    <row r="57" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V56" s="3"/>
+      <c r="W56" s="3"/>
+    </row>
+    <row r="57" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>11900</v>
+      </c>
+      <c r="E57" s="3">
+        <v>13200</v>
+      </c>
+      <c r="F57" s="3">
         <v>11600</v>
       </c>
-      <c r="E57" s="3">
+      <c r="G57" s="3">
         <v>11600</v>
       </c>
-      <c r="F57" s="3">
+      <c r="H57" s="3">
         <v>10500</v>
       </c>
-      <c r="G57" s="3">
+      <c r="I57" s="3">
         <v>14400</v>
       </c>
-      <c r="H57" s="3">
+      <c r="J57" s="3">
         <v>10800</v>
       </c>
-      <c r="I57" s="3">
+      <c r="K57" s="3">
         <v>10500</v>
       </c>
-      <c r="J57" s="3">
+      <c r="L57" s="3">
         <v>6700</v>
       </c>
-      <c r="K57" s="3">
+      <c r="M57" s="3">
         <v>11400</v>
       </c>
-      <c r="L57" s="3">
+      <c r="N57" s="3">
         <v>2200</v>
       </c>
-      <c r="M57" s="3">
-        <v>0</v>
-      </c>
-      <c r="N57" s="3">
-        <v>0</v>
-      </c>
       <c r="O57" s="3">
+        <v>0</v>
+      </c>
+      <c r="P57" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q57" s="3">
         <v>100</v>
       </c>
-      <c r="P57" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q57" s="3">
-        <v>0</v>
-      </c>
-      <c r="R57" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S57" s="3" t="s">
-        <v>3</v>
+      <c r="R57" s="3">
+        <v>0</v>
+      </c>
+      <c r="S57" s="3">
+        <v>0</v>
       </c>
       <c r="T57" s="3" t="s">
         <v>3</v>
@@ -3327,8 +3588,14 @@
       <c r="U57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V57" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -3386,126 +3653,144 @@
       <c r="U58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V58" s="3">
+        <v>0</v>
+      </c>
+      <c r="W58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>48200</v>
+      </c>
+      <c r="E59" s="3">
+        <v>27500</v>
+      </c>
+      <c r="F59" s="3">
         <v>24400</v>
       </c>
-      <c r="E59" s="3">
+      <c r="G59" s="3">
         <v>24500</v>
       </c>
-      <c r="F59" s="3">
+      <c r="H59" s="3">
         <v>28600</v>
       </c>
-      <c r="G59" s="3">
+      <c r="I59" s="3">
         <v>26500</v>
       </c>
-      <c r="H59" s="3">
+      <c r="J59" s="3">
         <v>24500</v>
       </c>
-      <c r="I59" s="3">
+      <c r="K59" s="3">
         <v>23000</v>
       </c>
-      <c r="J59" s="3">
+      <c r="L59" s="3">
         <v>17400</v>
       </c>
-      <c r="K59" s="3">
+      <c r="M59" s="3">
         <v>14000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="N59" s="3">
         <v>19500</v>
       </c>
-      <c r="M59" s="3">
+      <c r="O59" s="3">
         <v>2700</v>
       </c>
-      <c r="N59" s="3">
+      <c r="P59" s="3">
         <v>1800</v>
       </c>
-      <c r="O59" s="3">
-        <v>0</v>
-      </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
+        <v>0</v>
+      </c>
+      <c r="R59" s="3">
         <v>100</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="S59" s="3">
         <v>200</v>
       </c>
-      <c r="R59" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T59" s="3" t="s">
         <v>3</v>
       </c>
       <c r="U59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>60100</v>
+      </c>
+      <c r="E60" s="3">
+        <v>40700</v>
+      </c>
+      <c r="F60" s="3">
         <v>36000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="G60" s="3">
         <v>36200</v>
       </c>
-      <c r="F60" s="3">
+      <c r="H60" s="3">
         <v>39100</v>
       </c>
-      <c r="G60" s="3">
+      <c r="I60" s="3">
         <v>41000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="J60" s="3">
         <v>35300</v>
       </c>
-      <c r="I60" s="3">
+      <c r="K60" s="3">
         <v>33500</v>
       </c>
-      <c r="J60" s="3">
+      <c r="L60" s="3">
         <v>24000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="M60" s="3">
         <v>25400</v>
       </c>
-      <c r="L60" s="3">
+      <c r="N60" s="3">
         <v>21700</v>
       </c>
-      <c r="M60" s="3">
+      <c r="O60" s="3">
         <v>2700</v>
       </c>
-      <c r="N60" s="3">
+      <c r="P60" s="3">
         <v>1800</v>
       </c>
-      <c r="O60" s="3">
+      <c r="Q60" s="3">
         <v>100</v>
       </c>
-      <c r="P60" s="3">
+      <c r="R60" s="3">
         <v>200</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="S60" s="3">
         <v>200</v>
       </c>
-      <c r="R60" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T60" s="3" t="s">
         <v>3</v>
       </c>
       <c r="U60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V60" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -3563,56 +3848,62 @@
       <c r="U61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V61" s="3">
+        <v>0</v>
+      </c>
+      <c r="W61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>43700</v>
+      </c>
+      <c r="E62" s="3">
+        <v>45600</v>
+      </c>
+      <c r="F62" s="3">
         <v>50800</v>
       </c>
-      <c r="E62" s="3">
+      <c r="G62" s="3">
         <v>49600</v>
       </c>
-      <c r="F62" s="3">
+      <c r="H62" s="3">
         <v>50700</v>
       </c>
-      <c r="G62" s="3">
+      <c r="I62" s="3">
         <v>52400</v>
       </c>
-      <c r="H62" s="3">
+      <c r="J62" s="3">
         <v>58600</v>
       </c>
-      <c r="I62" s="3">
+      <c r="K62" s="3">
         <v>56200</v>
       </c>
-      <c r="J62" s="3">
+      <c r="L62" s="3">
         <v>51200</v>
       </c>
-      <c r="K62" s="3">
+      <c r="M62" s="3">
         <v>67700</v>
       </c>
-      <c r="L62" s="3">
+      <c r="N62" s="3">
         <v>89300</v>
       </c>
-      <c r="M62" s="3">
+      <c r="O62" s="3">
         <v>27100</v>
       </c>
-      <c r="N62" s="3">
+      <c r="P62" s="3">
         <v>30200</v>
       </c>
-      <c r="O62" s="3">
+      <c r="Q62" s="3">
         <v>25400</v>
       </c>
-      <c r="P62" s="3">
+      <c r="R62" s="3">
         <v>7500</v>
       </c>
-      <c r="Q62" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S62" s="3" t="s">
         <v>3</v>
       </c>
@@ -3622,8 +3913,14 @@
       <c r="U62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3681,8 +3978,14 @@
       <c r="U63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V63" s="3">
+        <v>0</v>
+      </c>
+      <c r="W63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3740,8 +4043,14 @@
       <c r="U64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V64" s="3">
+        <v>0</v>
+      </c>
+      <c r="W64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3799,67 +4108,79 @@
       <c r="U65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V65" s="3">
+        <v>0</v>
+      </c>
+      <c r="W65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>103700</v>
+      </c>
+      <c r="E66" s="3">
+        <v>86300</v>
+      </c>
+      <c r="F66" s="3">
         <v>86800</v>
       </c>
-      <c r="E66" s="3">
+      <c r="G66" s="3">
         <v>85800</v>
       </c>
-      <c r="F66" s="3">
+      <c r="H66" s="3">
         <v>89800</v>
       </c>
-      <c r="G66" s="3">
+      <c r="I66" s="3">
         <v>93400</v>
       </c>
-      <c r="H66" s="3">
+      <c r="J66" s="3">
         <v>93800</v>
       </c>
-      <c r="I66" s="3">
+      <c r="K66" s="3">
         <v>89800</v>
       </c>
-      <c r="J66" s="3">
+      <c r="L66" s="3">
         <v>75300</v>
       </c>
-      <c r="K66" s="3">
+      <c r="M66" s="3">
         <v>93100</v>
       </c>
-      <c r="L66" s="3">
+      <c r="N66" s="3">
         <v>111000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="O66" s="3">
         <v>29900</v>
       </c>
-      <c r="N66" s="3">
+      <c r="P66" s="3">
         <v>32000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="Q66" s="3">
         <v>25600</v>
       </c>
-      <c r="P66" s="3">
+      <c r="R66" s="3">
         <v>7700</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="S66" s="3">
         <v>200</v>
       </c>
-      <c r="R66" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T66" s="3" t="s">
         <v>3</v>
       </c>
       <c r="U66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V66" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3881,8 +4202,10 @@
       <c r="S67" s="3"/>
       <c r="T67" s="3"/>
       <c r="U67" s="3"/>
-    </row>
-    <row r="68" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V67" s="3"/>
+      <c r="W67" s="3"/>
+    </row>
+    <row r="68" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3940,8 +4263,14 @@
       <c r="U68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V68" s="3">
+        <v>0</v>
+      </c>
+      <c r="W68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3999,8 +4328,14 @@
       <c r="U69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V69" s="3">
+        <v>0</v>
+      </c>
+      <c r="W69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -4058,8 +4393,14 @@
       <c r="U70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V70" s="3">
+        <v>0</v>
+      </c>
+      <c r="W70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4117,58 +4458,64 @@
       <c r="U71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V71" s="3">
+        <v>0</v>
+      </c>
+      <c r="W71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-240600</v>
+      </c>
+      <c r="E72" s="3">
+        <v>-204700</v>
+      </c>
+      <c r="F72" s="3">
         <v>-190500</v>
       </c>
-      <c r="E72" s="3">
+      <c r="G72" s="3">
         <v>-139100</v>
       </c>
-      <c r="F72" s="3">
+      <c r="H72" s="3">
         <v>-120100</v>
       </c>
-      <c r="G72" s="3">
+      <c r="I72" s="3">
         <v>-101100</v>
       </c>
-      <c r="H72" s="3">
+      <c r="J72" s="3">
         <v>-90400</v>
       </c>
-      <c r="I72" s="3">
+      <c r="K72" s="3">
         <v>-67400</v>
       </c>
-      <c r="J72" s="3">
+      <c r="L72" s="3">
         <v>-71500</v>
       </c>
-      <c r="K72" s="3">
+      <c r="M72" s="3">
         <v>-75700</v>
       </c>
-      <c r="L72" s="3">
+      <c r="N72" s="3">
         <v>-79000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="O72" s="3">
         <v>-7600</v>
       </c>
-      <c r="N72" s="3">
+      <c r="P72" s="3">
         <v>-9500</v>
       </c>
-      <c r="O72" s="3">
+      <c r="Q72" s="3">
         <v>-2600</v>
       </c>
-      <c r="P72" s="3">
+      <c r="R72" s="3">
         <v>-200</v>
       </c>
-      <c r="Q72" s="3">
-        <v>0</v>
-      </c>
-      <c r="R72" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S72" s="3" t="s">
-        <v>3</v>
+      <c r="S72" s="3">
+        <v>0</v>
       </c>
       <c r="T72" s="3" t="s">
         <v>3</v>
@@ -4176,8 +4523,14 @@
       <c r="U72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V72" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -4235,8 +4588,14 @@
       <c r="U73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V73" s="3">
+        <v>0</v>
+      </c>
+      <c r="W73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -4294,8 +4653,14 @@
       <c r="U74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V74" s="3">
+        <v>0</v>
+      </c>
+      <c r="W74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -4353,58 +4718,64 @@
       <c r="U75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V75" s="3">
+        <v>0</v>
+      </c>
+      <c r="W75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>127900</v>
+      </c>
+      <c r="E76" s="3">
+        <v>161600</v>
+      </c>
+      <c r="F76" s="3">
         <v>170600</v>
       </c>
-      <c r="E76" s="3">
+      <c r="G76" s="3">
         <v>219100</v>
       </c>
-      <c r="F76" s="3">
+      <c r="H76" s="3">
         <v>238100</v>
       </c>
-      <c r="G76" s="3">
+      <c r="I76" s="3">
         <v>252600</v>
       </c>
-      <c r="H76" s="3">
+      <c r="J76" s="3">
         <v>258100</v>
       </c>
-      <c r="I76" s="3">
+      <c r="K76" s="3">
         <v>266400</v>
       </c>
-      <c r="J76" s="3">
+      <c r="L76" s="3">
         <v>254400</v>
       </c>
-      <c r="K76" s="3">
+      <c r="M76" s="3">
         <v>244200</v>
       </c>
-      <c r="L76" s="3">
+      <c r="N76" s="3">
         <v>233100</v>
       </c>
-      <c r="M76" s="3">
+      <c r="O76" s="3">
         <v>185800</v>
       </c>
-      <c r="N76" s="3">
+      <c r="P76" s="3">
         <v>183900</v>
       </c>
-      <c r="O76" s="3">
+      <c r="Q76" s="3">
         <v>190700</v>
       </c>
-      <c r="P76" s="3">
+      <c r="R76" s="3">
         <v>208800</v>
       </c>
-      <c r="Q76" s="3">
-        <v>0</v>
-      </c>
-      <c r="R76" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S76" s="3" t="s">
-        <v>3</v>
+      <c r="S76" s="3">
+        <v>0</v>
       </c>
       <c r="T76" s="3" t="s">
         <v>3</v>
@@ -4412,8 +4783,14 @@
       <c r="U76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V76" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -4471,122 +4848,134 @@
       <c r="U77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V77" s="3">
+        <v>0</v>
+      </c>
+      <c r="W77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:23" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E80" s="2">
+        <v>45291</v>
+      </c>
+      <c r="F80" s="2">
         <v>45199</v>
       </c>
-      <c r="E80" s="2">
+      <c r="G80" s="2">
         <v>45107</v>
       </c>
-      <c r="F80" s="2">
+      <c r="H80" s="2">
         <v>45016</v>
       </c>
-      <c r="G80" s="2">
+      <c r="I80" s="2">
         <v>44926</v>
       </c>
-      <c r="H80" s="2">
+      <c r="J80" s="2">
         <v>44834</v>
       </c>
-      <c r="I80" s="2">
+      <c r="K80" s="2">
         <v>44742</v>
       </c>
-      <c r="J80" s="2">
+      <c r="L80" s="2">
         <v>44651</v>
       </c>
-      <c r="K80" s="2">
+      <c r="M80" s="2">
         <v>44561</v>
       </c>
-      <c r="L80" s="2">
+      <c r="N80" s="2">
         <v>44469</v>
       </c>
-      <c r="M80" s="2">
+      <c r="O80" s="2">
         <v>44377</v>
       </c>
-      <c r="N80" s="2">
+      <c r="P80" s="2">
         <v>44286</v>
       </c>
-      <c r="O80" s="2">
+      <c r="Q80" s="2">
         <v>44196</v>
       </c>
-      <c r="P80" s="2">
+      <c r="R80" s="2">
         <v>44104</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="S80" s="2">
         <v>44012</v>
       </c>
-      <c r="R80" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="S80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="T80" s="2" t="s">
         <v>3</v>
       </c>
       <c r="U80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V80" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="W80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-35900</v>
+      </c>
+      <c r="E81" s="3">
+        <v>-14200</v>
+      </c>
+      <c r="F81" s="3">
         <v>-51400</v>
       </c>
-      <c r="E81" s="3">
+      <c r="G81" s="3">
         <v>-19000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="H81" s="3">
         <v>-19000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="I81" s="3">
         <v>-10700</v>
       </c>
-      <c r="H81" s="3">
+      <c r="J81" s="3">
         <v>-23000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="K81" s="3">
         <v>4100</v>
       </c>
-      <c r="J81" s="3">
+      <c r="L81" s="3">
         <v>4200</v>
       </c>
-      <c r="K81" s="3">
+      <c r="M81" s="3">
         <v>3300</v>
       </c>
-      <c r="L81" s="3">
+      <c r="N81" s="3">
         <v>21700</v>
       </c>
-      <c r="M81" s="3">
+      <c r="O81" s="3">
         <v>-21100</v>
       </c>
-      <c r="N81" s="3">
+      <c r="P81" s="3">
         <v>-6900</v>
       </c>
-      <c r="O81" s="3">
+      <c r="Q81" s="3">
         <v>-2400</v>
       </c>
-      <c r="P81" s="3">
+      <c r="R81" s="3">
         <v>-200</v>
       </c>
-      <c r="Q81" s="3">
-        <v>0</v>
-      </c>
-      <c r="R81" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S81" s="3" t="s">
-        <v>3</v>
+      <c r="S81" s="3">
+        <v>0</v>
       </c>
       <c r="T81" s="3" t="s">
         <v>3</v>
@@ -4594,8 +4983,14 @@
       <c r="U81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V81" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -4617,41 +5012,43 @@
       <c r="S82" s="3"/>
       <c r="T82" s="3"/>
       <c r="U82" s="3"/>
-    </row>
-    <row r="83" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V82" s="3"/>
+      <c r="W82" s="3"/>
+    </row>
+    <row r="83" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>3100</v>
+      </c>
+      <c r="E83" s="3">
+        <v>3100</v>
+      </c>
+      <c r="F83" s="3">
         <v>2900</v>
       </c>
-      <c r="E83" s="3">
+      <c r="G83" s="3">
         <v>4200</v>
       </c>
-      <c r="F83" s="3">
+      <c r="H83" s="3">
         <v>2400</v>
       </c>
-      <c r="G83" s="3">
+      <c r="I83" s="3">
         <v>2900</v>
       </c>
-      <c r="H83" s="3">
+      <c r="J83" s="3">
         <v>2700</v>
       </c>
-      <c r="I83" s="3">
+      <c r="K83" s="3">
         <v>2500</v>
       </c>
-      <c r="J83" s="3">
+      <c r="L83" s="3">
         <v>1200</v>
       </c>
-      <c r="K83" s="3">
+      <c r="M83" s="3">
         <v>500</v>
       </c>
-      <c r="L83" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M83" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N83" s="3" t="s">
         <v>3</v>
       </c>
@@ -4661,11 +5058,11 @@
       <c r="P83" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q83" s="3">
-        <v>0</v>
-      </c>
-      <c r="R83" s="3">
-        <v>0</v>
+      <c r="Q83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R83" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="S83" s="3">
         <v>0</v>
@@ -4676,8 +5073,14 @@
       <c r="U83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V83" s="3">
+        <v>0</v>
+      </c>
+      <c r="W83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -4735,8 +5138,14 @@
       <c r="U84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V84" s="3">
+        <v>0</v>
+      </c>
+      <c r="W84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -4794,8 +5203,14 @@
       <c r="U85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V85" s="3">
+        <v>0</v>
+      </c>
+      <c r="W85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -4853,8 +5268,14 @@
       <c r="U86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V86" s="3">
+        <v>0</v>
+      </c>
+      <c r="W86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -4912,8 +5333,14 @@
       <c r="U87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V87" s="3">
+        <v>0</v>
+      </c>
+      <c r="W87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -4971,55 +5398,61 @@
       <c r="U88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V88" s="3">
+        <v>0</v>
+      </c>
+      <c r="W88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-7400</v>
+      </c>
+      <c r="E89" s="3">
+        <v>-8900</v>
+      </c>
+      <c r="F89" s="3">
         <v>-9300</v>
       </c>
-      <c r="E89" s="3">
+      <c r="G89" s="3">
         <v>-15200</v>
       </c>
-      <c r="F89" s="3">
+      <c r="H89" s="3">
         <v>-15500</v>
       </c>
-      <c r="G89" s="3">
+      <c r="I89" s="3">
         <v>-8200</v>
       </c>
-      <c r="H89" s="3">
+      <c r="J89" s="3">
         <v>-23700</v>
       </c>
-      <c r="I89" s="3">
+      <c r="K89" s="3">
         <v>-22300</v>
       </c>
-      <c r="J89" s="3">
+      <c r="L89" s="3">
         <v>-19200</v>
       </c>
-      <c r="K89" s="3">
+      <c r="M89" s="3">
         <v>-6900</v>
       </c>
-      <c r="L89" s="3">
+      <c r="N89" s="3">
         <v>-38200</v>
       </c>
-      <c r="M89" s="3">
+      <c r="O89" s="3">
         <v>-600</v>
-      </c>
-      <c r="N89" s="3">
-        <v>-400</v>
-      </c>
-      <c r="O89" s="3">
-        <v>-200</v>
       </c>
       <c r="P89" s="3">
         <v>-400</v>
       </c>
-      <c r="Q89" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R89" s="3" t="s">
-        <v>3</v>
+      <c r="Q89" s="3">
+        <v>-200</v>
+      </c>
+      <c r="R89" s="3">
+        <v>-400</v>
       </c>
       <c r="S89" s="3" t="s">
         <v>3</v>
@@ -5030,8 +5463,14 @@
       <c r="U89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -5053,55 +5492,57 @@
       <c r="S90" s="3"/>
       <c r="T90" s="3"/>
       <c r="U90" s="3"/>
-    </row>
-    <row r="91" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V90" s="3"/>
+      <c r="W90" s="3"/>
+    </row>
+    <row r="91" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
-        <v>0</v>
+        <v>-1300</v>
       </c>
       <c r="E91" s="3">
+        <v>-1400</v>
+      </c>
+      <c r="F91" s="3">
+        <v>0</v>
+      </c>
+      <c r="G91" s="3">
         <v>-500</v>
       </c>
-      <c r="F91" s="3">
+      <c r="H91" s="3">
         <v>-1600</v>
       </c>
-      <c r="G91" s="3">
+      <c r="I91" s="3">
         <v>-5400</v>
       </c>
-      <c r="H91" s="3">
+      <c r="J91" s="3">
         <v>-4500</v>
       </c>
-      <c r="I91" s="3">
+      <c r="K91" s="3">
         <v>-700</v>
       </c>
-      <c r="J91" s="3">
+      <c r="L91" s="3">
         <v>-800</v>
       </c>
-      <c r="K91" s="3">
+      <c r="M91" s="3">
         <v>-1500</v>
       </c>
-      <c r="L91" s="3">
-        <v>0</v>
-      </c>
-      <c r="M91" s="3">
-        <v>0</v>
-      </c>
-      <c r="N91" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O91" s="3" t="s">
-        <v>3</v>
+      <c r="N91" s="3">
+        <v>0</v>
+      </c>
+      <c r="O91" s="3">
+        <v>0</v>
       </c>
       <c r="P91" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q91" s="3">
-        <v>0</v>
-      </c>
-      <c r="R91" s="3">
-        <v>0</v>
+      <c r="Q91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R91" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="S91" s="3">
         <v>0</v>
@@ -5112,8 +5553,14 @@
       <c r="U91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V91" s="3">
+        <v>0</v>
+      </c>
+      <c r="W91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -5171,8 +5618,14 @@
       <c r="U92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V92" s="3">
+        <v>0</v>
+      </c>
+      <c r="W92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -5230,58 +5683,64 @@
       <c r="U93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V93" s="3">
+        <v>0</v>
+      </c>
+      <c r="W93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-1300</v>
+      </c>
+      <c r="E94" s="3">
+        <v>27700</v>
+      </c>
+      <c r="F94" s="3">
         <v>22000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="G94" s="3">
         <v>10500</v>
       </c>
-      <c r="F94" s="3">
+      <c r="H94" s="3">
         <v>-18100</v>
       </c>
-      <c r="G94" s="3">
+      <c r="I94" s="3">
         <v>-49300</v>
       </c>
-      <c r="H94" s="3">
+      <c r="J94" s="3">
         <v>-38100</v>
       </c>
-      <c r="I94" s="3">
+      <c r="K94" s="3">
         <v>-2800</v>
       </c>
-      <c r="J94" s="3">
+      <c r="L94" s="3">
         <v>-800</v>
       </c>
-      <c r="K94" s="3">
+      <c r="M94" s="3">
         <v>-1500</v>
       </c>
-      <c r="L94" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N94" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O94" s="3">
-        <v>0</v>
+      <c r="O94" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="P94" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q94" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R94" s="3">
-        <v>0</v>
-      </c>
-      <c r="S94" s="3">
-        <v>0</v>
+      <c r="Q94" s="3">
+        <v>0</v>
+      </c>
+      <c r="R94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S94" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="T94" s="3">
         <v>0</v>
@@ -5289,8 +5748,14 @@
       <c r="U94" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="95" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V94" s="3">
+        <v>0</v>
+      </c>
+      <c r="W94" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -5312,8 +5777,10 @@
       <c r="S95" s="3"/>
       <c r="T95" s="3"/>
       <c r="U95" s="3"/>
-    </row>
-    <row r="96" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V95" s="3"/>
+      <c r="W95" s="3"/>
+    </row>
+    <row r="96" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -5371,8 +5838,14 @@
       <c r="U96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V96" s="3">
+        <v>0</v>
+      </c>
+      <c r="W96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -5430,8 +5903,14 @@
       <c r="U97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V97" s="3">
+        <v>0</v>
+      </c>
+      <c r="W97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -5489,8 +5968,14 @@
       <c r="U98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V98" s="3">
+        <v>0</v>
+      </c>
+      <c r="W98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -5548,8 +6033,14 @@
       <c r="U99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V99" s="3">
+        <v>0</v>
+      </c>
+      <c r="W99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
@@ -5557,44 +6048,44 @@
         <v>-200</v>
       </c>
       <c r="E100" s="3">
+        <v>-200</v>
+      </c>
+      <c r="F100" s="3">
+        <v>-200</v>
+      </c>
+      <c r="G100" s="3">
         <v>-300</v>
       </c>
-      <c r="F100" s="3">
+      <c r="H100" s="3">
         <v>100</v>
       </c>
-      <c r="G100" s="3">
-        <v>0</v>
-      </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
+        <v>0</v>
+      </c>
+      <c r="J100" s="3">
         <v>400</v>
       </c>
-      <c r="I100" s="3">
+      <c r="K100" s="3">
         <v>600</v>
       </c>
-      <c r="J100" s="3">
+      <c r="L100" s="3">
         <v>600</v>
       </c>
-      <c r="K100" s="3">
+      <c r="M100" s="3">
         <v>200</v>
       </c>
-      <c r="L100" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N100" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O100" s="3">
+      <c r="O100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q100" s="3">
         <v>100</v>
       </c>
-      <c r="P100" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R100" s="3" t="s">
         <v>3</v>
       </c>
@@ -5607,8 +6098,14 @@
       <c r="U100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -5616,19 +6113,19 @@
         <v>0</v>
       </c>
       <c r="E101" s="3">
+        <v>0</v>
+      </c>
+      <c r="F101" s="3">
+        <v>0</v>
+      </c>
+      <c r="G101" s="3">
         <v>-100</v>
       </c>
-      <c r="F101" s="3">
-        <v>0</v>
-      </c>
-      <c r="G101" s="3">
-        <v>0</v>
-      </c>
-      <c r="H101" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I101" s="3" t="s">
-        <v>3</v>
+      <c r="H101" s="3">
+        <v>0</v>
+      </c>
+      <c r="I101" s="3">
+        <v>0</v>
       </c>
       <c r="J101" s="3" t="s">
         <v>3</v>
@@ -5642,11 +6139,11 @@
       <c r="M101" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N101" s="3">
-        <v>0</v>
-      </c>
-      <c r="O101" s="3">
-        <v>0</v>
+      <c r="N101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O101" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="P101" s="3">
         <v>0</v>
@@ -5666,56 +6163,62 @@
       <c r="U101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V101" s="3">
+        <v>0</v>
+      </c>
+      <c r="W101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-8900</v>
+      </c>
+      <c r="E102" s="3">
+        <v>18700</v>
+      </c>
+      <c r="F102" s="3">
         <v>12500</v>
       </c>
-      <c r="E102" s="3">
+      <c r="G102" s="3">
         <v>-5000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="H102" s="3">
         <v>-33600</v>
       </c>
-      <c r="G102" s="3">
+      <c r="I102" s="3">
         <v>-57600</v>
       </c>
-      <c r="H102" s="3">
+      <c r="J102" s="3">
         <v>-61400</v>
       </c>
-      <c r="I102" s="3">
+      <c r="K102" s="3">
         <v>-24500</v>
       </c>
-      <c r="J102" s="3">
+      <c r="L102" s="3">
         <v>-19500</v>
       </c>
-      <c r="K102" s="3">
+      <c r="M102" s="3">
         <v>-8100</v>
       </c>
-      <c r="L102" s="3">
+      <c r="N102" s="3">
         <v>238600</v>
       </c>
-      <c r="M102" s="3">
+      <c r="O102" s="3">
         <v>-600</v>
       </c>
-      <c r="N102" s="3">
+      <c r="P102" s="3">
         <v>-400</v>
       </c>
-      <c r="O102" s="3">
+      <c r="Q102" s="3">
         <v>-100</v>
       </c>
-      <c r="P102" s="3">
+      <c r="R102" s="3">
         <v>1100</v>
       </c>
-      <c r="Q102" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S102" s="3" t="s">
         <v>3</v>
       </c>
@@ -5723,6 +6226,12 @@
         <v>3</v>
       </c>
       <c r="U102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/MKFG_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/MKFG_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="340" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="341" uniqueCount="92">
   <si>
     <t>MKFG</t>
   </si>
@@ -656,93 +656,94 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:W102"/>
+  <dimension ref="A5:X102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="23" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="24" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:24" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E7" s="2">
         <v>45382</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45291</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45199</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45107</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45016</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44926</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44834</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44742</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44651</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44561</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44469</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44377</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44286</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44196</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44104</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44012</v>
       </c>
-      <c r="T7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="U7" s="2" t="s">
         <v>3</v>
       </c>
@@ -752,50 +753,53 @@
       <c r="W7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>21700</v>
+      </c>
+      <c r="E8" s="3">
         <v>20500</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>24200</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>20100</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>25400</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>24100</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>29700</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>25200</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>24200</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>21900</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>26600</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>24000</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>40500</v>
       </c>
-      <c r="P8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q8" s="3" t="s">
         <v>3</v>
       </c>
@@ -808,8 +812,8 @@
       <c r="T8" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="U8" s="3">
-        <v>0</v>
+      <c r="U8" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="V8" s="3">
         <v>0</v>
@@ -817,50 +821,53 @@
       <c r="W8" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X8" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>10800</v>
+      </c>
+      <c r="E9" s="3">
         <v>10400</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>12500</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>10900</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>13500</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>12500</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>15700</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>13000</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>11300</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>10300</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>11600</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>10300</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>16400</v>
       </c>
-      <c r="P9" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q9" s="3" t="s">
         <v>3</v>
       </c>
@@ -882,50 +889,53 @@
       <c r="W9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>10900</v>
+      </c>
+      <c r="E10" s="3">
         <v>10100</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>11700</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>9200</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>11900</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>11600</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>14000</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>12200</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>12900</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>11600</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>15000</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>13700</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>24100</v>
       </c>
-      <c r="P10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q10" s="3" t="s">
         <v>3</v>
       </c>
@@ -947,8 +957,11 @@
       <c r="W10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -972,50 +985,51 @@
       <c r="U11" s="3"/>
       <c r="V11" s="3"/>
       <c r="W11" s="3"/>
-    </row>
-    <row r="12" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X11" s="3"/>
+    </row>
+    <row r="12" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>9100</v>
+      </c>
+      <c r="E12" s="3">
         <v>9900</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>10300</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>9700</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>10300</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>10400</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>11000</v>
-      </c>
-      <c r="J12" s="3">
-        <v>10400</v>
       </c>
       <c r="K12" s="3">
         <v>10400</v>
       </c>
       <c r="L12" s="3">
+        <v>10400</v>
+      </c>
+      <c r="M12" s="3">
         <v>10600</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>10700</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>9800</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>11700</v>
       </c>
-      <c r="P12" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q12" s="3" t="s">
         <v>3</v>
       </c>
@@ -1037,8 +1051,11 @@
       <c r="W12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1102,26 +1119,29 @@
       <c r="W13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>0</v>
+      </c>
+      <c r="E14" s="3">
         <v>17300</v>
       </c>
-      <c r="E14" s="3">
-        <v>0</v>
-      </c>
       <c r="F14" s="3">
+        <v>0</v>
+      </c>
+      <c r="G14" s="3">
         <v>29500</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>4000</v>
       </c>
-      <c r="H14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I14" s="3" t="s">
         <v>3</v>
       </c>
@@ -1134,8 +1154,8 @@
       <c r="L14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M14" s="3">
-        <v>0</v>
+      <c r="M14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N14" s="3">
         <v>0</v>
@@ -1167,8 +1187,11 @@
       <c r="W14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1232,8 +1255,11 @@
       <c r="W15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:24" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1254,61 +1280,62 @@
       <c r="U16" s="3"/>
       <c r="V16" s="3"/>
       <c r="W16" s="3"/>
-    </row>
-    <row r="17" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X16" s="3"/>
+    </row>
+    <row r="17" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>38700</v>
+      </c>
+      <c r="E17" s="3">
         <v>57700</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>43500</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>70500</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>45500</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>45600</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>49000</v>
-      </c>
-      <c r="J17" s="3">
-        <v>48000</v>
       </c>
       <c r="K17" s="3">
         <v>48000</v>
       </c>
       <c r="L17" s="3">
+        <v>48000</v>
+      </c>
+      <c r="M17" s="3">
         <v>43000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>45600</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>46400</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>60300</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>2100</v>
-      </c>
-      <c r="Q17" s="3">
-        <v>200</v>
       </c>
       <c r="R17" s="3">
         <v>200</v>
       </c>
       <c r="S17" s="3">
-        <v>0</v>
-      </c>
-      <c r="T17" s="3" t="s">
-        <v>3</v>
+        <v>200</v>
+      </c>
+      <c r="T17" s="3">
+        <v>0</v>
       </c>
       <c r="U17" s="3" t="s">
         <v>3</v>
@@ -1319,50 +1346,53 @@
       <c r="W17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-17000</v>
+      </c>
+      <c r="E18" s="3">
         <v>-37200</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-19300</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-50400</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-20100</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-21500</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-19300</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-22800</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-23800</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-21100</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-19000</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-22400</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-19800</v>
       </c>
-      <c r="P18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q18" s="3" t="s">
         <v>3</v>
       </c>
@@ -1384,8 +1414,11 @@
       <c r="W18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1409,50 +1442,51 @@
       <c r="U19" s="3"/>
       <c r="V19" s="3"/>
       <c r="W19" s="3"/>
-    </row>
-    <row r="20" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X19" s="3"/>
+    </row>
+    <row r="20" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>2500</v>
+      </c>
+      <c r="E20" s="3">
         <v>1200</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>5300</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-1100</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>900</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>2500</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>8100</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-100</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>27900</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>25300</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>22300</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>44100</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-1300</v>
       </c>
-      <c r="P20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q20" s="3" t="s">
         <v>3</v>
       </c>
@@ -1474,44 +1508,47 @@
       <c r="W20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-11400</v>
+      </c>
+      <c r="E21" s="3">
         <v>-32900</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>-10900</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-48600</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>-15000</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>-16600</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>-8300</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-20300</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>6600</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>5400</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>3800</v>
       </c>
-      <c r="N21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O21" s="3" t="s">
         <v>3</v>
       </c>
@@ -1539,8 +1576,11 @@
       <c r="W21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1548,7 +1588,7 @@
         <v>200</v>
       </c>
       <c r="E22" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="F22" s="3">
         <v>100</v>
@@ -1556,11 +1596,11 @@
       <c r="G22" s="3">
         <v>100</v>
       </c>
-      <c r="H22" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I22" s="3">
-        <v>0</v>
+      <c r="H22" s="3">
+        <v>100</v>
+      </c>
+      <c r="I22" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="J22" s="3">
         <v>0</v>
@@ -1580,8 +1620,8 @@
       <c r="O22" s="3">
         <v>0</v>
       </c>
-      <c r="P22" s="3" t="s">
-        <v>3</v>
+      <c r="P22" s="3">
+        <v>0</v>
       </c>
       <c r="Q22" s="3" t="s">
         <v>3</v>
@@ -1595,8 +1635,8 @@
       <c r="T22" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="U22" s="3">
-        <v>0</v>
+      <c r="U22" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="V22" s="3">
         <v>0</v>
@@ -1604,61 +1644,64 @@
       <c r="W22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-14700</v>
+      </c>
+      <c r="E23" s="3">
         <v>-36100</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-14200</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-51600</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-19300</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-19000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-11200</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-23000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>4100</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>4200</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>3300</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>21700</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-21100</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-6900</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-2400</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-200</v>
       </c>
-      <c r="S23" s="3">
-        <v>0</v>
-      </c>
-      <c r="T23" s="3" t="s">
-        <v>3</v>
+      <c r="T23" s="3">
+        <v>0</v>
       </c>
       <c r="U23" s="3" t="s">
         <v>3</v>
@@ -1669,32 +1712,35 @@
       <c r="W23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>-300</v>
+      </c>
+      <c r="E24" s="3">
         <v>-200</v>
       </c>
-      <c r="E24" s="3">
-        <v>0</v>
-      </c>
       <c r="F24" s="3">
+        <v>0</v>
+      </c>
+      <c r="G24" s="3">
         <v>-200</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>-400</v>
       </c>
-      <c r="H24" s="3">
-        <v>0</v>
-      </c>
       <c r="I24" s="3">
+        <v>0</v>
+      </c>
+      <c r="J24" s="3">
         <v>-400</v>
       </c>
-      <c r="J24" s="3">
-        <v>0</v>
-      </c>
       <c r="K24" s="3">
         <v>0</v>
       </c>
@@ -1702,16 +1748,16 @@
         <v>0</v>
       </c>
       <c r="M24" s="3">
+        <v>0</v>
+      </c>
+      <c r="N24" s="3">
         <v>100</v>
       </c>
-      <c r="N24" s="3">
-        <v>0</v>
-      </c>
       <c r="O24" s="3">
         <v>0</v>
       </c>
-      <c r="P24" s="3" t="s">
-        <v>3</v>
+      <c r="P24" s="3">
+        <v>0</v>
       </c>
       <c r="Q24" s="3" t="s">
         <v>3</v>
@@ -1725,8 +1771,8 @@
       <c r="T24" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="U24" s="3">
-        <v>0</v>
+      <c r="U24" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="V24" s="3">
         <v>0</v>
@@ -1734,8 +1780,11 @@
       <c r="W24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1799,61 +1848,64 @@
       <c r="W25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-14400</v>
+      </c>
+      <c r="E26" s="3">
         <v>-35900</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-14200</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-51400</v>
-      </c>
-      <c r="G26" s="3">
-        <v>-19000</v>
       </c>
       <c r="H26" s="3">
         <v>-19000</v>
       </c>
       <c r="I26" s="3">
+        <v>-19000</v>
+      </c>
+      <c r="J26" s="3">
         <v>-10700</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-23000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>4100</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>4200</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>3300</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>21700</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-21100</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-6900</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-2400</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-200</v>
       </c>
-      <c r="S26" s="3">
-        <v>0</v>
-      </c>
-      <c r="T26" s="3" t="s">
-        <v>3</v>
+      <c r="T26" s="3">
+        <v>0</v>
       </c>
       <c r="U26" s="3" t="s">
         <v>3</v>
@@ -1864,61 +1916,64 @@
       <c r="W26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-14400</v>
+      </c>
+      <c r="E27" s="3">
         <v>-35900</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-14200</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-51400</v>
-      </c>
-      <c r="G27" s="3">
-        <v>-19000</v>
       </c>
       <c r="H27" s="3">
         <v>-19000</v>
       </c>
       <c r="I27" s="3">
+        <v>-19000</v>
+      </c>
+      <c r="J27" s="3">
         <v>-10700</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-23000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>4100</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>4200</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>3300</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>21700</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-21100</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-6900</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-2400</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-200</v>
       </c>
-      <c r="S27" s="3">
-        <v>0</v>
-      </c>
-      <c r="T27" s="3" t="s">
-        <v>3</v>
+      <c r="T27" s="3">
+        <v>0</v>
       </c>
       <c r="U27" s="3" t="s">
         <v>3</v>
@@ -1929,8 +1984,11 @@
       <c r="W27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1994,8 +2052,11 @@
       <c r="W28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2059,8 +2120,11 @@
       <c r="W29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2124,8 +2188,11 @@
       <c r="W30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2189,50 +2256,53 @@
       <c r="W31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-2500</v>
+      </c>
+      <c r="E32" s="3">
         <v>-1200</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-5300</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>1100</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-900</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-2500</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-8100</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>100</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-27900</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-25300</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-22300</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-44100</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>1300</v>
       </c>
-      <c r="P32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q32" s="3" t="s">
         <v>3</v>
       </c>
@@ -2254,61 +2324,64 @@
       <c r="W32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-14400</v>
+      </c>
+      <c r="E33" s="3">
         <v>-35900</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-14200</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-51400</v>
-      </c>
-      <c r="G33" s="3">
-        <v>-19000</v>
       </c>
       <c r="H33" s="3">
         <v>-19000</v>
       </c>
       <c r="I33" s="3">
+        <v>-19000</v>
+      </c>
+      <c r="J33" s="3">
         <v>-10700</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-23000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>4100</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>4200</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>3300</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>21700</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-21100</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-6900</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-2400</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-200</v>
       </c>
-      <c r="S33" s="3">
-        <v>0</v>
-      </c>
-      <c r="T33" s="3" t="s">
-        <v>3</v>
+      <c r="T33" s="3">
+        <v>0</v>
       </c>
       <c r="U33" s="3" t="s">
         <v>3</v>
@@ -2319,8 +2392,11 @@
       <c r="W33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2384,61 +2460,64 @@
       <c r="W34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-14400</v>
+      </c>
+      <c r="E35" s="3">
         <v>-35900</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-14200</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-51400</v>
-      </c>
-      <c r="G35" s="3">
-        <v>-19000</v>
       </c>
       <c r="H35" s="3">
         <v>-19000</v>
       </c>
       <c r="I35" s="3">
+        <v>-19000</v>
+      </c>
+      <c r="J35" s="3">
         <v>-10700</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-23000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>4100</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>4200</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>3300</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>21700</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-21100</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-6900</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-2400</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-200</v>
       </c>
-      <c r="S35" s="3">
-        <v>0</v>
-      </c>
-      <c r="T35" s="3" t="s">
-        <v>3</v>
+      <c r="T35" s="3">
+        <v>0</v>
       </c>
       <c r="U35" s="3" t="s">
         <v>3</v>
@@ -2449,67 +2528,70 @@
       <c r="W35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:24" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E38" s="2">
         <v>45382</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45291</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45199</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45107</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45016</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44926</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44834</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44742</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44651</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44561</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44469</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44377</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44286</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44196</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44104</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44012</v>
       </c>
-      <c r="T38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="U38" s="2" t="s">
         <v>3</v>
       </c>
@@ -2519,8 +2601,11 @@
       <c r="W38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2544,8 +2629,9 @@
       <c r="U39" s="3"/>
       <c r="V39" s="3"/>
       <c r="W39" s="3"/>
-    </row>
-    <row r="40" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X39" s="3"/>
+    </row>
+    <row r="40" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2569,59 +2655,60 @@
       <c r="U40" s="3"/>
       <c r="V40" s="3"/>
       <c r="W40" s="3"/>
-    </row>
-    <row r="41" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X40" s="3"/>
+    </row>
+    <row r="41" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>73400</v>
+      </c>
+      <c r="E41" s="3">
         <v>107900</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>116900</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>98200</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>85700</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>90700</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>124200</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>181800</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>243200</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>269100</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>288600</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>296700</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>300</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>500</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>900</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>1100</v>
       </c>
-      <c r="S41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T41" s="3" t="s">
         <v>3</v>
       </c>
@@ -2634,32 +2721,35 @@
       <c r="W41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E42" s="3">
-        <v>0</v>
+      <c r="E42" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="F42" s="3">
+        <v>0</v>
+      </c>
+      <c r="G42" s="3">
         <v>27800</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>50400</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>60800</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>43700</v>
       </c>
-      <c r="J42" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K42" s="3" t="s">
         <v>3</v>
       </c>
@@ -2675,8 +2765,8 @@
       <c r="O42" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P42" s="3">
-        <v>0</v>
+      <c r="P42" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Q42" s="3">
         <v>0</v>
@@ -2699,47 +2789,50 @@
       <c r="W42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>21600</v>
+      </c>
+      <c r="E43" s="3">
         <v>21500</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>24100</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>22300</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>27100</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>26100</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>29300</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>30100</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>26600</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>22800</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>26800</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>24100</v>
       </c>
-      <c r="O43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P43" s="3" t="s">
         <v>3</v>
       </c>
@@ -2755,8 +2848,8 @@
       <c r="T43" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="U43" s="3">
-        <v>0</v>
+      <c r="U43" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="V43" s="3">
         <v>0</v>
@@ -2764,47 +2857,50 @@
       <c r="W43" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>22600</v>
+      </c>
+      <c r="E44" s="3">
         <v>23800</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>26800</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>28700</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>29600</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>29300</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>26400</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>24600</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>19300</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>12800</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>10400</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>11300</v>
       </c>
-      <c r="O44" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P44" s="3" t="s">
         <v>3</v>
       </c>
@@ -2820,8 +2916,8 @@
       <c r="T44" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="U44" s="3">
-        <v>0</v>
+      <c r="U44" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="V44" s="3">
         <v>0</v>
@@ -2829,62 +2925,65 @@
       <c r="W44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>23100</v>
+      </c>
+      <c r="E45" s="3">
         <v>5100</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>4800</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>5500</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>4300</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>5700</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>6200</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>6600</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>3900</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>5500</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>4400</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>5900</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>200</v>
-      </c>
-      <c r="P45" s="3">
-        <v>300</v>
       </c>
       <c r="Q45" s="3">
         <v>300</v>
       </c>
       <c r="R45" s="3">
+        <v>300</v>
+      </c>
+      <c r="S45" s="3">
         <v>400</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>200</v>
       </c>
-      <c r="T45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U45" s="3" t="s">
         <v>3</v>
       </c>
@@ -2894,62 +2993,65 @@
       <c r="W45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>140700</v>
+      </c>
+      <c r="E46" s="3">
         <v>158300</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>172500</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>182500</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>197000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>212500</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>229800</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>243100</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>293000</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>310300</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>330200</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>338000</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>600</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>800</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>1200</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>1400</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>200</v>
       </c>
-      <c r="T46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U46" s="3" t="s">
         <v>3</v>
       </c>
@@ -2959,8 +3061,11 @@
       <c r="W46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -2994,11 +3099,11 @@
       <c r="M47" s="3">
         <v>0</v>
       </c>
-      <c r="N47" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O47" s="3">
-        <v>215100</v>
+      <c r="N47" s="3">
+        <v>0</v>
+      </c>
+      <c r="O47" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="P47" s="3">
         <v>215100</v>
@@ -3007,11 +3112,11 @@
         <v>215100</v>
       </c>
       <c r="R47" s="3">
+        <v>215100</v>
+      </c>
+      <c r="S47" s="3">
         <v>215000</v>
       </c>
-      <c r="S47" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T47" s="3" t="s">
         <v>3</v>
       </c>
@@ -3024,47 +3129,50 @@
       <c r="W47" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="48" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X47" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="48" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>51800</v>
+      </c>
+      <c r="E48" s="3">
         <v>53700</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>54600</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>55300</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>57600</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>63700</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>64300</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>59000</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>53600</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>18400</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>6300</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>5300</v>
       </c>
-      <c r="O48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P48" s="3" t="s">
         <v>3</v>
       </c>
@@ -3080,8 +3188,8 @@
       <c r="T48" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="U48" s="3">
-        <v>0</v>
+      <c r="U48" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="V48" s="3">
         <v>0</v>
@@ -3089,38 +3197,41 @@
       <c r="W48" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="49" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X48" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>15600</v>
+      </c>
+      <c r="E49" s="3">
         <v>15900</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>17100</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>16200</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>46900</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>48600</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>48700</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>46600</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>6700</v>
       </c>
-      <c r="L49" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M49" s="3" t="s">
         <v>3</v>
       </c>
@@ -3133,8 +3244,8 @@
       <c r="P49" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q49" s="3">
-        <v>0</v>
+      <c r="Q49" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="R49" s="3">
         <v>0</v>
@@ -3154,8 +3265,11 @@
       <c r="W49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3219,8 +3333,11 @@
       <c r="W50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3284,46 +3401,49 @@
       <c r="W51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>3800</v>
+      </c>
+      <c r="E52" s="3">
         <v>3700</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>3800</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>3500</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>3300</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>3000</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>3100</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>3200</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>2900</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>1000</v>
-      </c>
-      <c r="M52" s="3">
-        <v>800</v>
       </c>
       <c r="N52" s="3">
         <v>800</v>
       </c>
-      <c r="O52" s="3" t="s">
-        <v>3</v>
+      <c r="O52" s="3">
+        <v>800</v>
       </c>
       <c r="P52" s="3" t="s">
         <v>3</v>
@@ -3340,8 +3460,8 @@
       <c r="T52" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="U52" s="3">
-        <v>0</v>
+      <c r="U52" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="V52" s="3">
         <v>0</v>
@@ -3349,8 +3469,11 @@
       <c r="W52" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="53" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X52" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3414,62 +3537,65 @@
       <c r="W53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>211800</v>
+      </c>
+      <c r="E54" s="3">
         <v>231600</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>248000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>257400</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>304900</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>327900</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>345900</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>351900</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>356100</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>329700</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>337300</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>344100</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>215700</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>215900</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>216300</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>216400</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>200</v>
       </c>
-      <c r="T54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U54" s="3" t="s">
         <v>3</v>
       </c>
@@ -3479,8 +3605,11 @@
       <c r="W54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3504,8 +3633,9 @@
       <c r="U55" s="3"/>
       <c r="V55" s="3"/>
       <c r="W55" s="3"/>
-    </row>
-    <row r="56" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X55" s="3"/>
+    </row>
+    <row r="56" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3529,61 +3659,62 @@
       <c r="U56" s="3"/>
       <c r="V56" s="3"/>
       <c r="W56" s="3"/>
-    </row>
-    <row r="57" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X56" s="3"/>
+    </row>
+    <row r="57" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>8700</v>
+      </c>
+      <c r="E57" s="3">
         <v>11900</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>13200</v>
-      </c>
-      <c r="F57" s="3">
-        <v>11600</v>
       </c>
       <c r="G57" s="3">
         <v>11600</v>
       </c>
       <c r="H57" s="3">
+        <v>11600</v>
+      </c>
+      <c r="I57" s="3">
         <v>10500</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>14400</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>10800</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>10500</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>6700</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>11400</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>2200</v>
       </c>
-      <c r="O57" s="3">
-        <v>0</v>
-      </c>
       <c r="P57" s="3">
         <v>0</v>
       </c>
       <c r="Q57" s="3">
+        <v>0</v>
+      </c>
+      <c r="R57" s="3">
         <v>100</v>
       </c>
-      <c r="R57" s="3">
-        <v>0</v>
-      </c>
       <c r="S57" s="3">
         <v>0</v>
       </c>
-      <c r="T57" s="3" t="s">
-        <v>3</v>
+      <c r="T57" s="3">
+        <v>0</v>
       </c>
       <c r="U57" s="3" t="s">
         <v>3</v>
@@ -3594,8 +3725,11 @@
       <c r="W57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -3659,62 +3793,65 @@
       <c r="W58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>45100</v>
+      </c>
+      <c r="E59" s="3">
         <v>48200</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>27500</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>24400</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>24500</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>28600</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>26500</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>24500</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>23000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>17400</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>14000</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>19500</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>2700</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>1800</v>
       </c>
-      <c r="Q59" s="3">
-        <v>0</v>
-      </c>
       <c r="R59" s="3">
+        <v>0</v>
+      </c>
+      <c r="S59" s="3">
         <v>100</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>200</v>
       </c>
-      <c r="T59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U59" s="3" t="s">
         <v>3</v>
       </c>
@@ -3724,61 +3861,64 @@
       <c r="W59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>53900</v>
+      </c>
+      <c r="E60" s="3">
         <v>60100</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>40700</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>36000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>36200</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>39100</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>41000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>35300</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>33500</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>24000</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>25400</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>21700</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>2700</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>1800</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>100</v>
-      </c>
-      <c r="R60" s="3">
-        <v>200</v>
       </c>
       <c r="S60" s="3">
         <v>200</v>
       </c>
-      <c r="T60" s="3" t="s">
-        <v>3</v>
+      <c r="T60" s="3">
+        <v>200</v>
       </c>
       <c r="U60" s="3" t="s">
         <v>3</v>
@@ -3789,8 +3929,11 @@
       <c r="W60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -3854,59 +3997,62 @@
       <c r="W61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>40500</v>
+      </c>
+      <c r="E62" s="3">
         <v>43700</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>45600</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>50800</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>49600</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>50700</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>52400</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>58600</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>56200</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>51200</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>67700</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>89300</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>27100</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>30200</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>25400</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>7500</v>
       </c>
-      <c r="S62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T62" s="3" t="s">
         <v>3</v>
       </c>
@@ -3919,8 +4065,11 @@
       <c r="W62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3984,8 +4133,11 @@
       <c r="W63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4049,8 +4201,11 @@
       <c r="W64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -4114,62 +4269,65 @@
       <c r="W65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>94400</v>
+      </c>
+      <c r="E66" s="3">
         <v>103700</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>86300</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>86800</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>85800</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>89800</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>93400</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>93800</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>89800</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>75300</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>93100</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>111000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>29900</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>32000</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>25600</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>7700</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>200</v>
       </c>
-      <c r="T66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U66" s="3" t="s">
         <v>3</v>
       </c>
@@ -4179,8 +4337,11 @@
       <c r="W66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4204,8 +4365,9 @@
       <c r="U67" s="3"/>
       <c r="V67" s="3"/>
       <c r="W67" s="3"/>
-    </row>
-    <row r="68" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X67" s="3"/>
+    </row>
+    <row r="68" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4269,8 +4431,11 @@
       <c r="W68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -4334,8 +4499,11 @@
       <c r="W69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -4399,8 +4567,11 @@
       <c r="W70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4464,61 +4635,64 @@
       <c r="W71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-255000</v>
+      </c>
+      <c r="E72" s="3">
         <v>-240600</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-204700</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-190500</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-139100</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-120100</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-101100</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-90400</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-67400</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-71500</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-75700</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-79000</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-7600</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-9500</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-2600</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-200</v>
       </c>
-      <c r="S72" s="3">
-        <v>0</v>
-      </c>
-      <c r="T72" s="3" t="s">
-        <v>3</v>
+      <c r="T72" s="3">
+        <v>0</v>
       </c>
       <c r="U72" s="3" t="s">
         <v>3</v>
@@ -4529,8 +4703,11 @@
       <c r="W72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -4594,8 +4771,11 @@
       <c r="W73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -4659,8 +4839,11 @@
       <c r="W74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -4724,61 +4907,64 @@
       <c r="W75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>117400</v>
+      </c>
+      <c r="E76" s="3">
         <v>127900</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>161600</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>170600</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>219100</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>238100</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>252600</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>258100</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>266400</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>254400</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>244200</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>233100</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>185800</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>183900</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>190700</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>208800</v>
       </c>
-      <c r="S76" s="3">
-        <v>0</v>
-      </c>
-      <c r="T76" s="3" t="s">
-        <v>3</v>
+      <c r="T76" s="3">
+        <v>0</v>
       </c>
       <c r="U76" s="3" t="s">
         <v>3</v>
@@ -4789,8 +4975,11 @@
       <c r="W76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -4854,67 +5043,70 @@
       <c r="W77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:24" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E80" s="2">
         <v>45382</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45291</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45199</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45107</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45016</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44926</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44834</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44742</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44651</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44561</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44469</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44377</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44286</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44196</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44104</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44012</v>
       </c>
-      <c r="T80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="U80" s="2" t="s">
         <v>3</v>
       </c>
@@ -4924,61 +5116,64 @@
       <c r="W80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-14400</v>
+      </c>
+      <c r="E81" s="3">
         <v>-35900</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-14200</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-51400</v>
-      </c>
-      <c r="G81" s="3">
-        <v>-19000</v>
       </c>
       <c r="H81" s="3">
         <v>-19000</v>
       </c>
       <c r="I81" s="3">
+        <v>-19000</v>
+      </c>
+      <c r="J81" s="3">
         <v>-10700</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-23000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>4100</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>4200</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>3300</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>21700</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-21100</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-6900</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-2400</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-200</v>
       </c>
-      <c r="S81" s="3">
-        <v>0</v>
-      </c>
-      <c r="T81" s="3" t="s">
-        <v>3</v>
+      <c r="T81" s="3">
+        <v>0</v>
       </c>
       <c r="U81" s="3" t="s">
         <v>3</v>
@@ -4989,8 +5184,11 @@
       <c r="W81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -5014,8 +5212,9 @@
       <c r="U82" s="3"/>
       <c r="V82" s="3"/>
       <c r="W82" s="3"/>
-    </row>
-    <row r="83" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X82" s="3"/>
+    </row>
+    <row r="83" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -5026,32 +5225,32 @@
         <v>3100</v>
       </c>
       <c r="F83" s="3">
+        <v>3100</v>
+      </c>
+      <c r="G83" s="3">
         <v>2900</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>4200</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>2400</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>2900</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>2700</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>2500</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>1200</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>500</v>
       </c>
-      <c r="N83" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O83" s="3" t="s">
         <v>3</v>
       </c>
@@ -5064,8 +5263,8 @@
       <c r="R83" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="S83" s="3">
-        <v>0</v>
+      <c r="S83" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="T83" s="3">
         <v>0</v>
@@ -5079,8 +5278,11 @@
       <c r="W83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -5144,8 +5346,11 @@
       <c r="W84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -5209,8 +5414,11 @@
       <c r="W85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -5274,8 +5482,11 @@
       <c r="W86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -5339,8 +5550,11 @@
       <c r="W87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -5404,59 +5618,62 @@
       <c r="W88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-14500</v>
+      </c>
+      <c r="E89" s="3">
         <v>-7400</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-8900</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-9300</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-15200</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-15500</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-8200</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-23700</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-22300</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-19200</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-6900</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-38200</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-600</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-400</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-200</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-400</v>
       </c>
-      <c r="S89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T89" s="3" t="s">
         <v>3</v>
       </c>
@@ -5469,8 +5686,11 @@
       <c r="W89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -5494,49 +5714,50 @@
       <c r="U90" s="3"/>
       <c r="V90" s="3"/>
       <c r="W90" s="3"/>
-    </row>
-    <row r="91" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X90" s="3"/>
+    </row>
+    <row r="91" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-200</v>
+      </c>
+      <c r="E91" s="3">
         <v>-1300</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-1400</v>
       </c>
-      <c r="F91" s="3">
-        <v>0</v>
-      </c>
       <c r="G91" s="3">
+        <v>0</v>
+      </c>
+      <c r="H91" s="3">
         <v>-500</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-1600</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-5400</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-4500</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-700</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-800</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-1500</v>
       </c>
-      <c r="N91" s="3">
-        <v>0</v>
-      </c>
       <c r="O91" s="3">
         <v>0</v>
       </c>
-      <c r="P91" s="3" t="s">
-        <v>3</v>
+      <c r="P91" s="3">
+        <v>0</v>
       </c>
       <c r="Q91" s="3" t="s">
         <v>3</v>
@@ -5544,8 +5765,8 @@
       <c r="R91" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="S91" s="3">
-        <v>0</v>
+      <c r="S91" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="T91" s="3">
         <v>0</v>
@@ -5559,8 +5780,11 @@
       <c r="W91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -5624,8 +5848,11 @@
       <c r="W92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -5689,61 +5916,64 @@
       <c r="W93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-200</v>
+      </c>
+      <c r="E94" s="3">
         <v>-1300</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>27700</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>22000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>10500</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-18100</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-49300</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-38100</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-2800</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-800</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-1500</v>
       </c>
-      <c r="N94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O94" s="3" t="s">
         <v>3</v>
       </c>
       <c r="P94" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q94" s="3">
-        <v>0</v>
-      </c>
-      <c r="R94" s="3" t="s">
-        <v>3</v>
+      <c r="Q94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R94" s="3">
+        <v>0</v>
       </c>
       <c r="S94" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="T94" s="3">
-        <v>0</v>
+      <c r="T94" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="U94" s="3">
         <v>0</v>
@@ -5754,8 +5984,11 @@
       <c r="W94" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="95" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X94" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -5779,8 +6012,9 @@
       <c r="U95" s="3"/>
       <c r="V95" s="3"/>
       <c r="W95" s="3"/>
-    </row>
-    <row r="96" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X95" s="3"/>
+    </row>
+    <row r="96" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -5844,8 +6078,11 @@
       <c r="W96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -5909,8 +6146,11 @@
       <c r="W97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -5974,8 +6214,11 @@
       <c r="W98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -6039,13 +6282,16 @@
       <c r="W99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
-        <v>-200</v>
+        <v>-700</v>
       </c>
       <c r="E100" s="3">
         <v>-200</v>
@@ -6054,41 +6300,41 @@
         <v>-200</v>
       </c>
       <c r="G100" s="3">
+        <v>-200</v>
+      </c>
+      <c r="H100" s="3">
         <v>-300</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>100</v>
       </c>
-      <c r="I100" s="3">
-        <v>0</v>
-      </c>
       <c r="J100" s="3">
+        <v>0</v>
+      </c>
+      <c r="K100" s="3">
         <v>400</v>
-      </c>
-      <c r="K100" s="3">
-        <v>600</v>
       </c>
       <c r="L100" s="3">
         <v>600</v>
       </c>
       <c r="M100" s="3">
+        <v>600</v>
+      </c>
+      <c r="N100" s="3">
         <v>200</v>
       </c>
-      <c r="N100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O100" s="3" t="s">
         <v>3</v>
       </c>
       <c r="P100" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="Q100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R100" s="3">
         <v>100</v>
       </c>
-      <c r="R100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S100" s="3" t="s">
         <v>3</v>
       </c>
@@ -6104,8 +6350,11 @@
       <c r="W100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -6119,16 +6368,16 @@
         <v>0</v>
       </c>
       <c r="G101" s="3">
+        <v>0</v>
+      </c>
+      <c r="H101" s="3">
         <v>-100</v>
       </c>
-      <c r="H101" s="3">
-        <v>0</v>
-      </c>
       <c r="I101" s="3">
         <v>0</v>
       </c>
-      <c r="J101" s="3" t="s">
-        <v>3</v>
+      <c r="J101" s="3">
+        <v>0</v>
       </c>
       <c r="K101" s="3" t="s">
         <v>3</v>
@@ -6145,8 +6394,8 @@
       <c r="O101" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P101" s="3">
-        <v>0</v>
+      <c r="P101" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Q101" s="3">
         <v>0</v>
@@ -6169,59 +6418,62 @@
       <c r="W101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-15400</v>
+      </c>
+      <c r="E102" s="3">
         <v>-8900</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>18700</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>12500</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-5000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-33600</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-57600</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-61400</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-24500</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-19500</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-8100</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>238600</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-600</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-400</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-100</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>1100</v>
       </c>
-      <c r="S102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T102" s="3" t="s">
         <v>3</v>
       </c>
@@ -6232,6 +6484,9 @@
         <v>3</v>
       </c>
       <c r="W102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/MKFG_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/MKFG_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="341" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="354" uniqueCount="92">
   <si>
     <t>MKFG</t>
   </si>
@@ -656,97 +656,98 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:X102"/>
+  <dimension ref="A5:Y102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="24" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="25" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:25" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E7" s="2">
         <v>45473</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45382</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45291</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45199</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45107</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45016</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44926</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44834</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44742</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44651</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44561</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44469</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44377</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44286</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44196</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44104</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44012</v>
       </c>
-      <c r="U7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="V7" s="2" t="s">
         <v>3</v>
       </c>
@@ -756,53 +757,56 @@
       <c r="X7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>20500</v>
+      </c>
+      <c r="E8" s="3">
         <v>21700</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>20500</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>24200</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>20100</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>25400</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>24100</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>29700</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>25200</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>24200</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>21900</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>26600</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>24000</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>40500</v>
       </c>
-      <c r="Q8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R8" s="3" t="s">
         <v>3</v>
       </c>
@@ -815,8 +819,8 @@
       <c r="U8" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="V8" s="3">
-        <v>0</v>
+      <c r="V8" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="W8" s="3">
         <v>0</v>
@@ -824,53 +828,56 @@
       <c r="X8" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y8" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>10400</v>
+      </c>
+      <c r="E9" s="3">
         <v>10800</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>10400</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>12500</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>10900</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>13500</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>12500</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>15700</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>13000</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>11300</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>10300</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>11600</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>10300</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>16400</v>
       </c>
-      <c r="Q9" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R9" s="3" t="s">
         <v>3</v>
       </c>
@@ -892,53 +899,56 @@
       <c r="X9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>10000</v>
+      </c>
+      <c r="E10" s="3">
         <v>10900</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>10100</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>11700</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>9200</v>
       </c>
-      <c r="H10" s="3">
-        <v>11900</v>
-      </c>
       <c r="I10" s="3">
+        <v>12000</v>
+      </c>
+      <c r="J10" s="3">
         <v>11600</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>14000</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>12200</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>12900</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>11600</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>15000</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>13700</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>24100</v>
       </c>
-      <c r="Q10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R10" s="3" t="s">
         <v>3</v>
       </c>
@@ -960,8 +970,11 @@
       <c r="X10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -986,53 +999,54 @@
       <c r="V11" s="3"/>
       <c r="W11" s="3"/>
       <c r="X11" s="3"/>
-    </row>
-    <row r="12" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y11" s="3"/>
+    </row>
+    <row r="12" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>7900</v>
+      </c>
+      <c r="E12" s="3">
         <v>9100</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>9900</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>10300</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>9700</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>10300</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>10400</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>11000</v>
-      </c>
-      <c r="K12" s="3">
-        <v>10400</v>
       </c>
       <c r="L12" s="3">
         <v>10400</v>
       </c>
       <c r="M12" s="3">
+        <v>10400</v>
+      </c>
+      <c r="N12" s="3">
         <v>10600</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>10700</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>9800</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>11700</v>
       </c>
-      <c r="Q12" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R12" s="3" t="s">
         <v>3</v>
       </c>
@@ -1054,8 +1068,11 @@
       <c r="X12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1122,31 +1139,34 @@
       <c r="X13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
-        <v>0</v>
+        <v>7300</v>
       </c>
       <c r="E14" s="3">
-        <v>17300</v>
+        <v>-1300</v>
       </c>
       <c r="F14" s="3">
-        <v>0</v>
+        <v>17500</v>
       </c>
       <c r="G14" s="3">
-        <v>29500</v>
+        <v>-3500</v>
       </c>
       <c r="H14" s="3">
-        <v>4000</v>
-      </c>
-      <c r="I14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J14" s="3" t="s">
-        <v>3</v>
+        <v>32000</v>
+      </c>
+      <c r="I14" s="3">
+        <v>800</v>
+      </c>
+      <c r="J14" s="3">
+        <v>-800</v>
       </c>
       <c r="K14" s="3" t="s">
         <v>3</v>
@@ -1157,8 +1177,8 @@
       <c r="M14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N14" s="3">
-        <v>0</v>
+      <c r="N14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="O14" s="3">
         <v>0</v>
@@ -1190,31 +1210,34 @@
       <c r="X14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>0</v>
+        <v>3100</v>
       </c>
       <c r="E15" s="3">
-        <v>0</v>
+        <v>3100</v>
       </c>
       <c r="F15" s="3">
-        <v>0</v>
+        <v>3100</v>
       </c>
       <c r="G15" s="3">
-        <v>0</v>
+        <v>3000</v>
       </c>
       <c r="H15" s="3">
-        <v>0</v>
+        <v>2900</v>
       </c>
       <c r="I15" s="3">
-        <v>0</v>
+        <v>4200</v>
       </c>
       <c r="J15" s="3">
-        <v>0</v>
+        <v>2400</v>
       </c>
       <c r="K15" s="3">
         <v>0</v>
@@ -1258,8 +1281,11 @@
       <c r="X15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:25" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1281,64 +1307,65 @@
       <c r="V16" s="3"/>
       <c r="W16" s="3"/>
       <c r="X16" s="3"/>
-    </row>
-    <row r="17" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y16" s="3"/>
+    </row>
+    <row r="17" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>37600</v>
+      </c>
+      <c r="E17" s="3">
         <v>38700</v>
       </c>
-      <c r="E17" s="3">
-        <v>57700</v>
-      </c>
       <c r="F17" s="3">
+        <v>40400</v>
+      </c>
+      <c r="G17" s="3">
         <v>43500</v>
       </c>
-      <c r="G17" s="3">
-        <v>70500</v>
-      </c>
       <c r="H17" s="3">
+        <v>41000</v>
+      </c>
+      <c r="I17" s="3">
         <v>45500</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>45600</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>49000</v>
-      </c>
-      <c r="K17" s="3">
-        <v>48000</v>
       </c>
       <c r="L17" s="3">
         <v>48000</v>
       </c>
       <c r="M17" s="3">
+        <v>48000</v>
+      </c>
+      <c r="N17" s="3">
         <v>43000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>45600</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>46400</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>60300</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>2100</v>
-      </c>
-      <c r="R17" s="3">
-        <v>200</v>
       </c>
       <c r="S17" s="3">
         <v>200</v>
       </c>
       <c r="T17" s="3">
-        <v>0</v>
-      </c>
-      <c r="U17" s="3" t="s">
-        <v>3</v>
+        <v>200</v>
+      </c>
+      <c r="U17" s="3">
+        <v>0</v>
       </c>
       <c r="V17" s="3" t="s">
         <v>3</v>
@@ -1349,53 +1376,56 @@
       <c r="X17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-17100</v>
+      </c>
+      <c r="E18" s="3">
         <v>-17000</v>
       </c>
-      <c r="E18" s="3">
-        <v>-37200</v>
-      </c>
       <c r="F18" s="3">
+        <v>-19800</v>
+      </c>
+      <c r="G18" s="3">
+        <v>-19400</v>
+      </c>
+      <c r="H18" s="3">
+        <v>-21000</v>
+      </c>
+      <c r="I18" s="3">
+        <v>-20100</v>
+      </c>
+      <c r="J18" s="3">
+        <v>-21500</v>
+      </c>
+      <c r="K18" s="3">
         <v>-19300</v>
       </c>
-      <c r="G18" s="3">
-        <v>-50400</v>
-      </c>
-      <c r="H18" s="3">
-        <v>-20100</v>
-      </c>
-      <c r="I18" s="3">
-        <v>-21500</v>
-      </c>
-      <c r="J18" s="3">
-        <v>-19300</v>
-      </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-22800</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-23800</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-21100</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-19000</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-22400</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-19800</v>
       </c>
-      <c r="Q18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R18" s="3" t="s">
         <v>3</v>
       </c>
@@ -1417,8 +1447,11 @@
       <c r="X18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1443,53 +1476,54 @@
       <c r="V19" s="3"/>
       <c r="W19" s="3"/>
       <c r="X19" s="3"/>
-    </row>
-    <row r="20" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y19" s="3"/>
+    </row>
+    <row r="20" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>2500</v>
+        <v>0</v>
       </c>
       <c r="E20" s="3">
-        <v>1200</v>
+        <v>0</v>
       </c>
       <c r="F20" s="3">
-        <v>5300</v>
+        <v>100</v>
       </c>
       <c r="G20" s="3">
-        <v>-1100</v>
+        <v>-200</v>
       </c>
       <c r="H20" s="3">
-        <v>900</v>
+        <v>100</v>
       </c>
       <c r="I20" s="3">
-        <v>2500</v>
+        <v>-100</v>
       </c>
       <c r="J20" s="3">
+        <v>0</v>
+      </c>
+      <c r="K20" s="3">
         <v>8100</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-100</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>27900</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>25300</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>22300</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>44100</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-1300</v>
       </c>
-      <c r="Q20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R20" s="3" t="s">
         <v>3</v>
       </c>
@@ -1511,47 +1545,50 @@
       <c r="X20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>-11400</v>
+        <v>-14100</v>
       </c>
       <c r="E21" s="3">
-        <v>-32900</v>
+        <v>-13900</v>
       </c>
       <c r="F21" s="3">
-        <v>-10900</v>
+        <v>-16800</v>
       </c>
       <c r="G21" s="3">
-        <v>-48600</v>
+        <v>-16100</v>
       </c>
       <c r="H21" s="3">
-        <v>-15000</v>
+        <v>-18200</v>
       </c>
       <c r="I21" s="3">
-        <v>-16600</v>
+        <v>-15700</v>
       </c>
       <c r="J21" s="3">
+        <v>-19100</v>
+      </c>
+      <c r="K21" s="3">
         <v>-8300</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-20300</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>6600</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>5400</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>3800</v>
       </c>
-      <c r="O21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P21" s="3" t="s">
         <v>3</v>
       </c>
@@ -1579,8 +1616,11 @@
       <c r="X21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1591,7 +1631,7 @@
         <v>200</v>
       </c>
       <c r="F22" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="G22" s="3">
         <v>100</v>
@@ -1599,11 +1639,11 @@
       <c r="H22" s="3">
         <v>100</v>
       </c>
-      <c r="I22" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J22" s="3">
-        <v>0</v>
+      <c r="I22" s="3">
+        <v>100</v>
+      </c>
+      <c r="J22" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K22" s="3">
         <v>0</v>
@@ -1623,8 +1663,8 @@
       <c r="P22" s="3">
         <v>0</v>
       </c>
-      <c r="Q22" s="3" t="s">
-        <v>3</v>
+      <c r="Q22" s="3">
+        <v>0</v>
       </c>
       <c r="R22" s="3" t="s">
         <v>3</v>
@@ -1638,8 +1678,8 @@
       <c r="U22" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="V22" s="3">
-        <v>0</v>
+      <c r="V22" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="W22" s="3">
         <v>0</v>
@@ -1647,64 +1687,67 @@
       <c r="X22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-23600</v>
+      </c>
+      <c r="E23" s="3">
         <v>-14700</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-36100</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-14200</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-51600</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-19300</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-19000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-11200</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-23000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>4100</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>4200</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>3300</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>21700</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-21100</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-6900</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-2400</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-200</v>
       </c>
-      <c r="T23" s="3">
-        <v>0</v>
-      </c>
-      <c r="U23" s="3" t="s">
-        <v>3</v>
+      <c r="U23" s="3">
+        <v>0</v>
       </c>
       <c r="V23" s="3" t="s">
         <v>3</v>
@@ -1715,35 +1758,38 @@
       <c r="X23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>-200</v>
+      </c>
+      <c r="E24" s="3">
         <v>-300</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>-200</v>
       </c>
-      <c r="F24" s="3">
-        <v>0</v>
-      </c>
       <c r="G24" s="3">
+        <v>0</v>
+      </c>
+      <c r="H24" s="3">
         <v>-200</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>-400</v>
       </c>
-      <c r="I24" s="3">
-        <v>0</v>
-      </c>
       <c r="J24" s="3">
+        <v>0</v>
+      </c>
+      <c r="K24" s="3">
         <v>-400</v>
       </c>
-      <c r="K24" s="3">
-        <v>0</v>
-      </c>
       <c r="L24" s="3">
         <v>0</v>
       </c>
@@ -1751,16 +1797,16 @@
         <v>0</v>
       </c>
       <c r="N24" s="3">
+        <v>0</v>
+      </c>
+      <c r="O24" s="3">
         <v>100</v>
       </c>
-      <c r="O24" s="3">
-        <v>0</v>
-      </c>
       <c r="P24" s="3">
         <v>0</v>
       </c>
-      <c r="Q24" s="3" t="s">
-        <v>3</v>
+      <c r="Q24" s="3">
+        <v>0</v>
       </c>
       <c r="R24" s="3" t="s">
         <v>3</v>
@@ -1774,8 +1820,8 @@
       <c r="U24" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="V24" s="3">
-        <v>0</v>
+      <c r="V24" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="W24" s="3">
         <v>0</v>
@@ -1783,8 +1829,11 @@
       <c r="X24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1851,64 +1900,67 @@
       <c r="X25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-23400</v>
+      </c>
+      <c r="E26" s="3">
         <v>-14400</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-35900</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-14200</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-51400</v>
-      </c>
-      <c r="H26" s="3">
-        <v>-19000</v>
       </c>
       <c r="I26" s="3">
         <v>-19000</v>
       </c>
       <c r="J26" s="3">
+        <v>-19000</v>
+      </c>
+      <c r="K26" s="3">
         <v>-10700</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-23000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>4100</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>4200</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>3300</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>21700</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-21100</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-6900</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-2400</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-200</v>
       </c>
-      <c r="T26" s="3">
-        <v>0</v>
-      </c>
-      <c r="U26" s="3" t="s">
-        <v>3</v>
+      <c r="U26" s="3">
+        <v>0</v>
       </c>
       <c r="V26" s="3" t="s">
         <v>3</v>
@@ -1919,64 +1971,67 @@
       <c r="X26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-23400</v>
+      </c>
+      <c r="E27" s="3">
         <v>-14400</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-35900</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-14200</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-51400</v>
-      </c>
-      <c r="H27" s="3">
-        <v>-19000</v>
       </c>
       <c r="I27" s="3">
         <v>-19000</v>
       </c>
       <c r="J27" s="3">
+        <v>-19000</v>
+      </c>
+      <c r="K27" s="3">
         <v>-10700</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-23000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>4100</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>4200</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>3300</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>21700</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-21100</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-6900</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-2400</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-200</v>
       </c>
-      <c r="T27" s="3">
-        <v>0</v>
-      </c>
-      <c r="U27" s="3" t="s">
-        <v>3</v>
+      <c r="U27" s="3">
+        <v>0</v>
       </c>
       <c r="V27" s="3" t="s">
         <v>3</v>
@@ -1987,8 +2042,11 @@
       <c r="X27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2055,8 +2113,11 @@
       <c r="X28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2123,8 +2184,11 @@
       <c r="X29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2191,8 +2255,11 @@
       <c r="X30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2259,53 +2326,56 @@
       <c r="X31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>-2500</v>
+        <v>0</v>
       </c>
       <c r="E32" s="3">
-        <v>-1200</v>
+        <v>0</v>
       </c>
       <c r="F32" s="3">
-        <v>-5300</v>
+        <v>-100</v>
       </c>
       <c r="G32" s="3">
-        <v>1100</v>
+        <v>200</v>
       </c>
       <c r="H32" s="3">
-        <v>-900</v>
+        <v>-100</v>
       </c>
       <c r="I32" s="3">
-        <v>-2500</v>
+        <v>100</v>
       </c>
       <c r="J32" s="3">
+        <v>0</v>
+      </c>
+      <c r="K32" s="3">
         <v>-8100</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>100</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-27900</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-25300</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-22300</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-44100</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>1300</v>
       </c>
-      <c r="Q32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R32" s="3" t="s">
         <v>3</v>
       </c>
@@ -2327,64 +2397,67 @@
       <c r="X32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-23400</v>
+      </c>
+      <c r="E33" s="3">
         <v>-14400</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-35900</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-14200</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-51400</v>
-      </c>
-      <c r="H33" s="3">
-        <v>-19000</v>
       </c>
       <c r="I33" s="3">
         <v>-19000</v>
       </c>
       <c r="J33" s="3">
+        <v>-19000</v>
+      </c>
+      <c r="K33" s="3">
         <v>-10700</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-23000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>4100</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>4200</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>3300</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>21700</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-21100</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-6900</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-2400</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-200</v>
       </c>
-      <c r="T33" s="3">
-        <v>0</v>
-      </c>
-      <c r="U33" s="3" t="s">
-        <v>3</v>
+      <c r="U33" s="3">
+        <v>0</v>
       </c>
       <c r="V33" s="3" t="s">
         <v>3</v>
@@ -2395,8 +2468,11 @@
       <c r="X33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2463,64 +2539,67 @@
       <c r="X34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-23400</v>
+      </c>
+      <c r="E35" s="3">
         <v>-14400</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-35900</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-14200</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-51400</v>
-      </c>
-      <c r="H35" s="3">
-        <v>-19000</v>
       </c>
       <c r="I35" s="3">
         <v>-19000</v>
       </c>
       <c r="J35" s="3">
+        <v>-19000</v>
+      </c>
+      <c r="K35" s="3">
         <v>-10700</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-23000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>4100</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>4200</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>3300</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>21700</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-21100</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-6900</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-2400</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-200</v>
       </c>
-      <c r="T35" s="3">
-        <v>0</v>
-      </c>
-      <c r="U35" s="3" t="s">
-        <v>3</v>
+      <c r="U35" s="3">
+        <v>0</v>
       </c>
       <c r="V35" s="3" t="s">
         <v>3</v>
@@ -2531,70 +2610,73 @@
       <c r="X35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:25" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:24" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E38" s="2">
         <v>45473</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45382</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45291</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45199</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45107</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45016</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44926</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44834</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44742</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44651</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44561</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44469</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44377</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44286</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44196</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44104</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44012</v>
       </c>
-      <c r="U38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="V38" s="2" t="s">
         <v>3</v>
       </c>
@@ -2604,8 +2686,11 @@
       <c r="X38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2630,8 +2715,9 @@
       <c r="V39" s="3"/>
       <c r="W39" s="3"/>
       <c r="X39" s="3"/>
-    </row>
-    <row r="40" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y39" s="3"/>
+    </row>
+    <row r="40" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2656,62 +2742,63 @@
       <c r="V40" s="3"/>
       <c r="W40" s="3"/>
       <c r="X40" s="3"/>
-    </row>
-    <row r="41" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y40" s="3"/>
+    </row>
+    <row r="41" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>59300</v>
+      </c>
+      <c r="E41" s="3">
         <v>73400</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>107900</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>116900</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>98200</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>85700</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>90700</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>124200</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>181800</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>243200</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>269100</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>288600</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>296700</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>300</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>500</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>900</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>1100</v>
       </c>
-      <c r="T41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U41" s="3" t="s">
         <v>3</v>
       </c>
@@ -2724,35 +2811,38 @@
       <c r="X41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="D42" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E42" s="3" t="s">
-        <v>3</v>
+      <c r="D42" s="3">
+        <v>0</v>
+      </c>
+      <c r="E42" s="3">
+        <v>0</v>
       </c>
       <c r="F42" s="3">
         <v>0</v>
       </c>
       <c r="G42" s="3">
+        <v>0</v>
+      </c>
+      <c r="H42" s="3">
         <v>27800</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>50400</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>60800</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>43700</v>
       </c>
-      <c r="K42" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L42" s="3" t="s">
         <v>3</v>
       </c>
@@ -2768,8 +2858,8 @@
       <c r="P42" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q42" s="3">
-        <v>0</v>
+      <c r="Q42" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="R42" s="3">
         <v>0</v>
@@ -2792,50 +2882,53 @@
       <c r="X42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>19900</v>
+      </c>
+      <c r="E43" s="3">
         <v>21600</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>21500</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>24100</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>22300</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>27100</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>26100</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>29300</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>30100</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>26600</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>22800</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>26800</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>24100</v>
       </c>
-      <c r="P43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q43" s="3" t="s">
         <v>3</v>
       </c>
@@ -2851,8 +2944,8 @@
       <c r="U43" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="V43" s="3">
-        <v>0</v>
+      <c r="V43" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="W43" s="3">
         <v>0</v>
@@ -2860,50 +2953,53 @@
       <c r="X43" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>21700</v>
+      </c>
+      <c r="E44" s="3">
         <v>22600</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>23800</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>26800</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>28700</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>29600</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>29300</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>26400</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>24600</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>19300</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>12800</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>10400</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>11300</v>
       </c>
-      <c r="P44" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q44" s="3" t="s">
         <v>3</v>
       </c>
@@ -2919,8 +3015,8 @@
       <c r="U44" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="V44" s="3">
-        <v>0</v>
+      <c r="V44" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="W44" s="3">
         <v>0</v>
@@ -2928,65 +3024,68 @@
       <c r="X44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>23100</v>
+        <v>2200</v>
       </c>
       <c r="E45" s="3">
-        <v>5100</v>
+        <v>1900</v>
       </c>
       <c r="F45" s="3">
-        <v>4800</v>
+        <v>1700</v>
       </c>
       <c r="G45" s="3">
+        <v>2000</v>
+      </c>
+      <c r="H45" s="3">
+        <v>3300</v>
+      </c>
+      <c r="I45" s="3">
+        <v>3300</v>
+      </c>
+      <c r="J45" s="3">
+        <v>3400</v>
+      </c>
+      <c r="K45" s="3">
+        <v>6200</v>
+      </c>
+      <c r="L45" s="3">
+        <v>6600</v>
+      </c>
+      <c r="M45" s="3">
+        <v>3900</v>
+      </c>
+      <c r="N45" s="3">
         <v>5500</v>
       </c>
-      <c r="H45" s="3">
-        <v>4300</v>
-      </c>
-      <c r="I45" s="3">
-        <v>5700</v>
-      </c>
-      <c r="J45" s="3">
-        <v>6200</v>
-      </c>
-      <c r="K45" s="3">
-        <v>6600</v>
-      </c>
-      <c r="L45" s="3">
-        <v>3900</v>
-      </c>
-      <c r="M45" s="3">
-        <v>5500</v>
-      </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>4400</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>5900</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>200</v>
-      </c>
-      <c r="Q45" s="3">
-        <v>300</v>
       </c>
       <c r="R45" s="3">
         <v>300</v>
       </c>
       <c r="S45" s="3">
+        <v>300</v>
+      </c>
+      <c r="T45" s="3">
         <v>400</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>200</v>
       </c>
-      <c r="U45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V45" s="3" t="s">
         <v>3</v>
       </c>
@@ -2996,65 +3095,68 @@
       <c r="X45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>125600</v>
+      </c>
+      <c r="E46" s="3">
         <v>140700</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>158300</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>172500</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>182500</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>197000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>212500</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>229800</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>243100</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>293000</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>310300</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>330200</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>338000</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>600</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>800</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>1200</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>1400</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>200</v>
       </c>
-      <c r="U46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V46" s="3" t="s">
         <v>3</v>
       </c>
@@ -3064,31 +3166,34 @@
       <c r="X46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="D47" s="3">
-        <v>0</v>
-      </c>
-      <c r="E47" s="3">
-        <v>0</v>
-      </c>
-      <c r="F47" s="3">
-        <v>0</v>
-      </c>
-      <c r="G47" s="3">
-        <v>0</v>
-      </c>
-      <c r="H47" s="3">
-        <v>0</v>
-      </c>
-      <c r="I47" s="3">
-        <v>0</v>
-      </c>
-      <c r="J47" s="3">
-        <v>0</v>
+      <c r="D47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J47" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K47" s="3">
         <v>0</v>
@@ -3102,11 +3207,11 @@
       <c r="N47" s="3">
         <v>0</v>
       </c>
-      <c r="O47" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P47" s="3">
-        <v>215100</v>
+      <c r="O47" s="3">
+        <v>0</v>
+      </c>
+      <c r="P47" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Q47" s="3">
         <v>215100</v>
@@ -3115,11 +3220,11 @@
         <v>215100</v>
       </c>
       <c r="S47" s="3">
+        <v>215100</v>
+      </c>
+      <c r="T47" s="3">
         <v>215000</v>
       </c>
-      <c r="T47" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U47" s="3" t="s">
         <v>3</v>
       </c>
@@ -3132,50 +3237,53 @@
       <c r="X47" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="48" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y47" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="48" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>47400</v>
+      </c>
+      <c r="E48" s="3">
         <v>51800</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>53700</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>54600</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>55300</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>57600</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>63700</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>64300</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>59000</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>53600</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>18400</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>6300</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>5300</v>
       </c>
-      <c r="P48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q48" s="3" t="s">
         <v>3</v>
       </c>
@@ -3191,8 +3299,8 @@
       <c r="U48" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="V48" s="3">
-        <v>0</v>
+      <c r="V48" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="W48" s="3">
         <v>0</v>
@@ -3200,41 +3308,44 @@
       <c r="X48" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="49" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y48" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>21300</v>
+      </c>
+      <c r="E49" s="3">
         <v>15600</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>15900</v>
       </c>
-      <c r="F49" s="3">
-        <v>17100</v>
-      </c>
       <c r="G49" s="3">
+        <v>18400</v>
+      </c>
+      <c r="H49" s="3">
         <v>16200</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>46900</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>48600</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>48700</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>46600</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>6700</v>
       </c>
-      <c r="M49" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N49" s="3" t="s">
         <v>3</v>
       </c>
@@ -3247,8 +3358,8 @@
       <c r="Q49" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R49" s="3">
-        <v>0</v>
+      <c r="R49" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="S49" s="3">
         <v>0</v>
@@ -3268,8 +3379,11 @@
       <c r="X49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3336,8 +3450,11 @@
       <c r="X50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3404,49 +3521,52 @@
       <c r="X51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>3000</v>
+      </c>
+      <c r="E52" s="3">
         <v>3800</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>3700</v>
       </c>
-      <c r="F52" s="3">
-        <v>3800</v>
-      </c>
       <c r="G52" s="3">
+        <v>2500</v>
+      </c>
+      <c r="H52" s="3">
         <v>3500</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>3300</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>3000</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>3100</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>3200</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>2900</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>1000</v>
-      </c>
-      <c r="N52" s="3">
-        <v>800</v>
       </c>
       <c r="O52" s="3">
         <v>800</v>
       </c>
-      <c r="P52" s="3" t="s">
-        <v>3</v>
+      <c r="P52" s="3">
+        <v>800</v>
       </c>
       <c r="Q52" s="3" t="s">
         <v>3</v>
@@ -3463,8 +3583,8 @@
       <c r="U52" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="V52" s="3">
-        <v>0</v>
+      <c r="V52" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="W52" s="3">
         <v>0</v>
@@ -3472,8 +3592,11 @@
       <c r="X52" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="53" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y52" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3540,65 +3663,68 @@
       <c r="X53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>197200</v>
+      </c>
+      <c r="E54" s="3">
         <v>211800</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>231600</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>248000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>257400</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>304900</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>327900</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>345900</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>351900</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>356100</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>329700</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>337300</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>344100</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>215700</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>215900</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>216300</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>216400</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>200</v>
       </c>
-      <c r="U54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V54" s="3" t="s">
         <v>3</v>
       </c>
@@ -3608,8 +3734,11 @@
       <c r="X54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3634,8 +3763,9 @@
       <c r="V55" s="3"/>
       <c r="W55" s="3"/>
       <c r="X55" s="3"/>
-    </row>
-    <row r="56" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y55" s="3"/>
+    </row>
+    <row r="56" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3660,64 +3790,65 @@
       <c r="V56" s="3"/>
       <c r="W56" s="3"/>
       <c r="X56" s="3"/>
-    </row>
-    <row r="57" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y56" s="3"/>
+    </row>
+    <row r="57" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>10300</v>
+      </c>
+      <c r="E57" s="3">
         <v>8700</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>11900</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>13200</v>
-      </c>
-      <c r="G57" s="3">
-        <v>11600</v>
       </c>
       <c r="H57" s="3">
         <v>11600</v>
       </c>
       <c r="I57" s="3">
+        <v>11600</v>
+      </c>
+      <c r="J57" s="3">
         <v>10500</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>14400</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>10800</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>10500</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>6700</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>11400</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>2200</v>
       </c>
-      <c r="P57" s="3">
-        <v>0</v>
-      </c>
       <c r="Q57" s="3">
         <v>0</v>
       </c>
       <c r="R57" s="3">
+        <v>0</v>
+      </c>
+      <c r="S57" s="3">
         <v>100</v>
       </c>
-      <c r="S57" s="3">
-        <v>0</v>
-      </c>
       <c r="T57" s="3">
         <v>0</v>
       </c>
-      <c r="U57" s="3" t="s">
-        <v>3</v>
+      <c r="U57" s="3">
+        <v>0</v>
       </c>
       <c r="V57" s="3" t="s">
         <v>3</v>
@@ -3728,31 +3859,34 @@
       <c r="X57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>0</v>
+        <v>5800</v>
       </c>
       <c r="E58" s="3">
-        <v>0</v>
+        <v>7400</v>
       </c>
       <c r="F58" s="3">
-        <v>0</v>
+        <v>7300</v>
       </c>
       <c r="G58" s="3">
-        <v>0</v>
+        <v>7400</v>
       </c>
       <c r="H58" s="3">
-        <v>0</v>
+        <v>7600</v>
       </c>
       <c r="I58" s="3">
-        <v>0</v>
+        <v>7800</v>
       </c>
       <c r="J58" s="3">
-        <v>0</v>
+        <v>8000</v>
       </c>
       <c r="K58" s="3">
         <v>0</v>
@@ -3796,65 +3930,68 @@
       <c r="X58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>45100</v>
+        <v>27400</v>
       </c>
       <c r="E59" s="3">
-        <v>48200</v>
+        <v>27600</v>
       </c>
       <c r="F59" s="3">
-        <v>27500</v>
+        <v>29700</v>
       </c>
       <c r="G59" s="3">
-        <v>24400</v>
+        <v>11400</v>
       </c>
       <c r="H59" s="3">
+        <v>9300</v>
+      </c>
+      <c r="I59" s="3">
+        <v>9500</v>
+      </c>
+      <c r="J59" s="3">
+        <v>10300</v>
+      </c>
+      <c r="K59" s="3">
+        <v>26500</v>
+      </c>
+      <c r="L59" s="3">
         <v>24500</v>
       </c>
-      <c r="I59" s="3">
-        <v>28600</v>
-      </c>
-      <c r="J59" s="3">
-        <v>26500</v>
-      </c>
-      <c r="K59" s="3">
-        <v>24500</v>
-      </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>23000</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>17400</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>14000</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>19500</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>2700</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>1800</v>
       </c>
-      <c r="R59" s="3">
-        <v>0</v>
-      </c>
       <c r="S59" s="3">
+        <v>0</v>
+      </c>
+      <c r="T59" s="3">
         <v>100</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>200</v>
       </c>
-      <c r="U59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V59" s="3" t="s">
         <v>3</v>
       </c>
@@ -3864,64 +4001,67 @@
       <c r="X59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>52500</v>
+      </c>
+      <c r="E60" s="3">
         <v>53900</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>60100</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>40700</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>36000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>36200</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>39100</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>41000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>35300</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>33500</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>24000</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>25400</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>21700</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>2700</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>1800</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>100</v>
-      </c>
-      <c r="S60" s="3">
-        <v>200</v>
       </c>
       <c r="T60" s="3">
         <v>200</v>
       </c>
-      <c r="U60" s="3" t="s">
-        <v>3</v>
+      <c r="U60" s="3">
+        <v>200</v>
       </c>
       <c r="V60" s="3" t="s">
         <v>3</v>
@@ -3932,31 +4072,34 @@
       <c r="X60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>0</v>
+        <v>27800</v>
       </c>
       <c r="E61" s="3">
-        <v>0</v>
+        <v>33400</v>
       </c>
       <c r="F61" s="3">
-        <v>0</v>
+        <v>34600</v>
       </c>
       <c r="G61" s="3">
-        <v>0</v>
+        <v>35800</v>
       </c>
       <c r="H61" s="3">
-        <v>0</v>
+        <v>37100</v>
       </c>
       <c r="I61" s="3">
-        <v>0</v>
+        <v>38200</v>
       </c>
       <c r="J61" s="3">
-        <v>0</v>
+        <v>39400</v>
       </c>
       <c r="K61" s="3">
         <v>0</v>
@@ -4000,62 +4143,65 @@
       <c r="X61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>40500</v>
+        <v>14300</v>
       </c>
       <c r="E62" s="3">
-        <v>43700</v>
+        <v>1900</v>
       </c>
       <c r="F62" s="3">
-        <v>45600</v>
+        <v>3600</v>
       </c>
       <c r="G62" s="3">
-        <v>50800</v>
+        <v>3700</v>
       </c>
       <c r="H62" s="3">
-        <v>49600</v>
+        <v>8000</v>
       </c>
       <c r="I62" s="3">
-        <v>50700</v>
+        <v>5700</v>
       </c>
       <c r="J62" s="3">
+        <v>5500</v>
+      </c>
+      <c r="K62" s="3">
         <v>52400</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>58600</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>56200</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>51200</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>67700</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>89300</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>27100</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>30200</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>25400</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>7500</v>
       </c>
-      <c r="T62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U62" s="3" t="s">
         <v>3</v>
       </c>
@@ -4068,8 +4214,11 @@
       <c r="X62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -4136,8 +4285,11 @@
       <c r="X63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4204,8 +4356,11 @@
       <c r="X64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -4272,65 +4427,68 @@
       <c r="X65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>99300</v>
+      </c>
+      <c r="E66" s="3">
         <v>94400</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>103700</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>86300</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>86800</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>85800</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>89800</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>93400</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>93800</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>89800</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>75300</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>93100</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>111000</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>29900</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>32000</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>25600</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>7700</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>200</v>
       </c>
-      <c r="U66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V66" s="3" t="s">
         <v>3</v>
       </c>
@@ -4340,8 +4498,11 @@
       <c r="X66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4366,8 +4527,9 @@
       <c r="V67" s="3"/>
       <c r="W67" s="3"/>
       <c r="X67" s="3"/>
-    </row>
-    <row r="68" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y67" s="3"/>
+    </row>
+    <row r="68" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4434,8 +4596,11 @@
       <c r="X68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -4502,8 +4667,11 @@
       <c r="X69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -4570,8 +4738,11 @@
       <c r="X70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4638,64 +4809,67 @@
       <c r="X71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-278400</v>
+      </c>
+      <c r="E72" s="3">
         <v>-255000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-240600</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-204700</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-190500</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-139100</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-120100</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-101100</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-90400</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-67400</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-71500</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-75700</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-79000</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-7600</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-9500</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-2600</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-200</v>
       </c>
-      <c r="T72" s="3">
-        <v>0</v>
-      </c>
-      <c r="U72" s="3" t="s">
-        <v>3</v>
+      <c r="U72" s="3">
+        <v>0</v>
       </c>
       <c r="V72" s="3" t="s">
         <v>3</v>
@@ -4706,8 +4880,11 @@
       <c r="X72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -4774,8 +4951,11 @@
       <c r="X73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -4842,8 +5022,11 @@
       <c r="X74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -4910,64 +5093,67 @@
       <c r="X75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>98000</v>
+      </c>
+      <c r="E76" s="3">
         <v>117400</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>127900</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>161600</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>170600</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>219100</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>238100</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>252600</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>258100</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>266400</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>254400</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>244200</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>233100</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>185800</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>183900</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>190700</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>208800</v>
       </c>
-      <c r="T76" s="3">
-        <v>0</v>
-      </c>
-      <c r="U76" s="3" t="s">
-        <v>3</v>
+      <c r="U76" s="3">
+        <v>0</v>
       </c>
       <c r="V76" s="3" t="s">
         <v>3</v>
@@ -4978,8 +5164,11 @@
       <c r="X76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -5046,70 +5235,73 @@
       <c r="X77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:25" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:24" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E80" s="2">
         <v>45473</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45382</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45291</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45199</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45107</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45016</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44926</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44834</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44742</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44651</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44561</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44469</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44377</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44286</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44196</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44104</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44012</v>
       </c>
-      <c r="U80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="V80" s="2" t="s">
         <v>3</v>
       </c>
@@ -5119,64 +5311,67 @@
       <c r="X80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-23400</v>
+      </c>
+      <c r="E81" s="3">
         <v>-14400</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-35900</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-14200</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-51400</v>
-      </c>
-      <c r="H81" s="3">
-        <v>-19000</v>
       </c>
       <c r="I81" s="3">
         <v>-19000</v>
       </c>
       <c r="J81" s="3">
+        <v>-19000</v>
+      </c>
+      <c r="K81" s="3">
         <v>-10700</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-23000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>4100</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>4200</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>3300</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>21700</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-21100</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-6900</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-2400</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-200</v>
       </c>
-      <c r="T81" s="3">
-        <v>0</v>
-      </c>
-      <c r="U81" s="3" t="s">
-        <v>3</v>
+      <c r="U81" s="3">
+        <v>0</v>
       </c>
       <c r="V81" s="3" t="s">
         <v>3</v>
@@ -5187,8 +5382,11 @@
       <c r="X81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -5213,47 +5411,48 @@
       <c r="V82" s="3"/>
       <c r="W82" s="3"/>
       <c r="X82" s="3"/>
-    </row>
-    <row r="83" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y82" s="3"/>
+    </row>
+    <row r="83" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>3100</v>
+        <v>2600</v>
       </c>
       <c r="E83" s="3">
-        <v>3100</v>
+        <v>4000</v>
       </c>
       <c r="F83" s="3">
-        <v>3100</v>
+        <v>2200</v>
       </c>
       <c r="G83" s="3">
+        <v>2800</v>
+      </c>
+      <c r="H83" s="3">
+        <v>2600</v>
+      </c>
+      <c r="I83" s="3">
+        <v>2500</v>
+      </c>
+      <c r="J83" s="3">
+        <v>1200</v>
+      </c>
+      <c r="K83" s="3">
         <v>2900</v>
       </c>
-      <c r="H83" s="3">
-        <v>4200</v>
-      </c>
-      <c r="I83" s="3">
-        <v>2400</v>
-      </c>
-      <c r="J83" s="3">
-        <v>2900</v>
-      </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>2700</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>2500</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>1200</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>500</v>
       </c>
-      <c r="O83" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P83" s="3" t="s">
         <v>3</v>
       </c>
@@ -5266,8 +5465,8 @@
       <c r="S83" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="T83" s="3">
-        <v>0</v>
+      <c r="T83" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="U83" s="3">
         <v>0</v>
@@ -5281,8 +5480,11 @@
       <c r="X83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -5349,8 +5551,11 @@
       <c r="X84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -5417,8 +5622,11 @@
       <c r="X85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -5485,8 +5693,11 @@
       <c r="X86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -5553,8 +5764,11 @@
       <c r="X87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -5621,62 +5835,65 @@
       <c r="X88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-14000</v>
+      </c>
+      <c r="E89" s="3">
         <v>-14500</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-7400</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-8900</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-9300</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-15200</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-15500</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-8200</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-23700</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-22300</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-19200</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-6900</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-38200</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-600</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-400</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-200</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>-400</v>
       </c>
-      <c r="T89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U89" s="3" t="s">
         <v>3</v>
       </c>
@@ -5689,8 +5906,11 @@
       <c r="X89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -5715,52 +5935,53 @@
       <c r="V90" s="3"/>
       <c r="W90" s="3"/>
       <c r="X90" s="3"/>
-    </row>
-    <row r="91" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y90" s="3"/>
+    </row>
+    <row r="91" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-400</v>
+      </c>
+      <c r="E91" s="3">
         <v>-200</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-1300</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-1400</v>
       </c>
-      <c r="G91" s="3">
-        <v>0</v>
-      </c>
       <c r="H91" s="3">
+        <v>0</v>
+      </c>
+      <c r="I91" s="3">
         <v>-500</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-1600</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-5400</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-4500</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-700</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-800</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-1500</v>
       </c>
-      <c r="O91" s="3">
-        <v>0</v>
-      </c>
       <c r="P91" s="3">
         <v>0</v>
       </c>
-      <c r="Q91" s="3" t="s">
-        <v>3</v>
+      <c r="Q91" s="3">
+        <v>0</v>
       </c>
       <c r="R91" s="3" t="s">
         <v>3</v>
@@ -5768,8 +5989,8 @@
       <c r="S91" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="T91" s="3">
-        <v>0</v>
+      <c r="T91" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="U91" s="3">
         <v>0</v>
@@ -5783,8 +6004,11 @@
       <c r="X91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -5851,8 +6075,11 @@
       <c r="X92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -5919,64 +6146,67 @@
       <c r="X93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-400</v>
+      </c>
+      <c r="E94" s="3">
         <v>-200</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-1300</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>27700</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>22000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>10500</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-18100</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-49300</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-38100</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-2800</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-800</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-1500</v>
       </c>
-      <c r="O94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P94" s="3" t="s">
         <v>3</v>
       </c>
       <c r="Q94" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R94" s="3">
-        <v>0</v>
-      </c>
-      <c r="S94" s="3" t="s">
-        <v>3</v>
+      <c r="R94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S94" s="3">
+        <v>0</v>
       </c>
       <c r="T94" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="U94" s="3">
-        <v>0</v>
+      <c r="U94" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="V94" s="3">
         <v>0</v>
@@ -5987,8 +6217,11 @@
       <c r="X94" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="95" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y94" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -6013,31 +6246,32 @@
       <c r="V95" s="3"/>
       <c r="W95" s="3"/>
       <c r="X95" s="3"/>
-    </row>
-    <row r="96" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y95" s="3"/>
+    </row>
+    <row r="96" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="D96" s="3">
-        <v>0</v>
-      </c>
-      <c r="E96" s="3">
-        <v>0</v>
-      </c>
-      <c r="F96" s="3">
-        <v>0</v>
-      </c>
-      <c r="G96" s="3">
-        <v>0</v>
-      </c>
-      <c r="H96" s="3">
-        <v>0</v>
-      </c>
-      <c r="I96" s="3">
-        <v>0</v>
-      </c>
-      <c r="J96" s="3">
-        <v>0</v>
+      <c r="D96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J96" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K96" s="3">
         <v>0</v>
@@ -6081,8 +6315,11 @@
       <c r="X96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -6149,8 +6386,11 @@
       <c r="X97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -6217,8 +6457,11 @@
       <c r="X98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -6285,16 +6528,19 @@
       <c r="X99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-100</v>
+      </c>
+      <c r="E100" s="3">
         <v>-700</v>
-      </c>
-      <c r="E100" s="3">
-        <v>-200</v>
       </c>
       <c r="F100" s="3">
         <v>-200</v>
@@ -6303,41 +6549,41 @@
         <v>-200</v>
       </c>
       <c r="H100" s="3">
+        <v>-200</v>
+      </c>
+      <c r="I100" s="3">
         <v>-300</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>100</v>
       </c>
-      <c r="J100" s="3">
-        <v>0</v>
-      </c>
       <c r="K100" s="3">
+        <v>0</v>
+      </c>
+      <c r="L100" s="3">
         <v>400</v>
-      </c>
-      <c r="L100" s="3">
-        <v>600</v>
       </c>
       <c r="M100" s="3">
         <v>600</v>
       </c>
       <c r="N100" s="3">
+        <v>600</v>
+      </c>
+      <c r="O100" s="3">
         <v>200</v>
       </c>
-      <c r="O100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P100" s="3" t="s">
         <v>3</v>
       </c>
       <c r="Q100" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R100" s="3">
+      <c r="R100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S100" s="3">
         <v>100</v>
       </c>
-      <c r="S100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T100" s="3" t="s">
         <v>3</v>
       </c>
@@ -6353,8 +6599,11 @@
       <c r="X100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -6362,7 +6611,7 @@
         <v>0</v>
       </c>
       <c r="E101" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="F101" s="3">
         <v>0</v>
@@ -6371,16 +6620,16 @@
         <v>0</v>
       </c>
       <c r="H101" s="3">
-        <v>-100</v>
-      </c>
-      <c r="I101" s="3">
-        <v>0</v>
-      </c>
-      <c r="J101" s="3">
-        <v>0</v>
-      </c>
-      <c r="K101" s="3" t="s">
-        <v>3</v>
+        <v>0</v>
+      </c>
+      <c r="I101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K101" s="3">
+        <v>0</v>
       </c>
       <c r="L101" s="3" t="s">
         <v>3</v>
@@ -6397,8 +6646,8 @@
       <c r="P101" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q101" s="3">
-        <v>0</v>
+      <c r="Q101" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="R101" s="3">
         <v>0</v>
@@ -6421,62 +6670,65 @@
       <c r="X101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-14500</v>
+      </c>
+      <c r="E102" s="3">
         <v>-15400</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-8900</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>18700</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>12500</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-5000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-33600</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-57600</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-61400</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-24500</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-19500</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-8100</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>238600</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-600</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-400</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-100</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>1100</v>
       </c>
-      <c r="T102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U102" s="3" t="s">
         <v>3</v>
       </c>
@@ -6487,6 +6739,9 @@
         <v>3</v>
       </c>
       <c r="X102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y102" s="3" t="s">
         <v>3</v>
       </c>
     </row>
